--- a/data/power_analysis.xlsx
+++ b/data/power_analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cristian/Dropbox/data_replication_centre/Cristian/power_analysis_study_2/reproducibility_power_analyses/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6D9179-3F53-8F47-A886-6F33433D466D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88815223-E087-6E43-BE3A-2E3A02E13E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="320" yWindow="820" windowWidth="28480" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3850" uniqueCount="1251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3870" uniqueCount="1256">
   <si>
     <t>study_title</t>
   </si>
@@ -3249,9 +3249,6 @@
   </si>
   <si>
     <t>females would show attenuated changes in NMF compared to males, particularly at the lowest intensity</t>
-  </si>
-  <si>
-    <t>We hypothesized that the acute preexercise ingestion of pure carnosine and anserine would improve performance of the Wingate tests, especially in situations where fatigue is induced</t>
   </si>
   <si>
     <t>We hypothesized that, consistent with the un-derlying biomechanical model, tibial IRT would be the more effective interms of pain reduction</t>
@@ -4406,6 +4403,36 @@
 Number of groups = 2
 Number of measurements  = 2
 Nonsphericity correction ε = 1</t>
+  </si>
+  <si>
+    <t>Ketone Monoester Ingestion Alters Metabolism and Simulated Rugby Performance in Professional Players</t>
+  </si>
+  <si>
+    <t>time-trial performance</t>
+  </si>
+  <si>
+    <t>A sample size estimation was performed based on data from Cox et al. (2016), whereby CHO + BHB-ME improved time-trial per-formance by 411 ± 458 s compared with CHO. Using this effect size (d= 0.90), 12 participants should provide greater than 80% power to detect such a difference with a two-tailed t test and an alpha level of .05.</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>It was hypothesized that ketone ester-CHO coingestion would augment simulated rugby union performance, when com-pared to isocaloric CHO ingestion
+"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t tests - Means: Difference between two dependent means (matched pairs)
+Analysis:	A priori: Compute required sample size 
+Input:		Tail(s)                       	=	Two
+			Effect size dz                	=	0,9
+			α err prob                    	=	0,05
+			Power (1-β err prob)          	=	0,8
+Output:		Noncentrality parameter δ     	=	3,1176915
+			Critical t                    	=	2,2009852
+			Df                            	=	11
+			Total sample size             	=	12
+			Actual power                  	=	0,8097855
+</t>
   </si>
 </sst>
 </file>
@@ -4634,203 +4661,202 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -5177,35 +5203,34 @@
     <col min="5" max="5" width="59" style="12" customWidth="1"/>
     <col min="6" max="6" width="16.1640625" style="27" customWidth="1"/>
     <col min="7" max="7" width="11" style="27" customWidth="1"/>
-    <col min="8" max="8" width="13.1640625" style="49" customWidth="1"/>
+    <col min="8" max="8" width="13.1640625" customWidth="1"/>
     <col min="9" max="9" width="19" style="27" customWidth="1"/>
     <col min="10" max="10" width="20.1640625" style="27" customWidth="1"/>
-    <col min="11" max="12" width="15.33203125" style="49" customWidth="1"/>
-    <col min="13" max="13" width="14.5" style="49" customWidth="1"/>
-    <col min="14" max="14" width="16.1640625" style="49" customWidth="1"/>
+    <col min="11" max="12" width="15.33203125" customWidth="1"/>
+    <col min="13" max="13" width="14.5" customWidth="1"/>
+    <col min="14" max="14" width="16.1640625" customWidth="1"/>
     <col min="15" max="15" width="15.33203125" style="27" customWidth="1"/>
-    <col min="16" max="16" width="14.5" style="51" customWidth="1"/>
-    <col min="17" max="17" width="11.33203125" style="49" customWidth="1"/>
+    <col min="16" max="16" width="14.5" style="50" customWidth="1"/>
+    <col min="17" max="17" width="11.33203125" customWidth="1"/>
     <col min="18" max="18" width="19.33203125" style="27" customWidth="1"/>
     <col min="19" max="19" width="23.1640625" style="27" customWidth="1"/>
     <col min="20" max="20" width="16.33203125" style="3" customWidth="1"/>
     <col min="21" max="22" width="27.33203125" style="3" customWidth="1"/>
     <col min="23" max="23" width="25.83203125" style="27" customWidth="1"/>
-    <col min="24" max="24" width="22.6640625" style="51" customWidth="1"/>
+    <col min="24" max="24" width="22.6640625" style="50" customWidth="1"/>
     <col min="25" max="28" width="19.33203125" style="27" customWidth="1"/>
-    <col min="29" max="29" width="20.33203125" style="51" customWidth="1"/>
+    <col min="29" max="29" width="20.33203125" style="50" customWidth="1"/>
     <col min="30" max="32" width="38.5" style="11" customWidth="1"/>
-    <col min="33" max="33" width="28.5" style="49" customWidth="1"/>
-    <col min="34" max="34" width="17.5" style="49" customWidth="1"/>
+    <col min="33" max="33" width="28.5" customWidth="1"/>
+    <col min="34" max="34" width="17.5" customWidth="1"/>
     <col min="35" max="36" width="19" style="3" customWidth="1"/>
     <col min="37" max="37" width="56.5" style="1" customWidth="1"/>
     <col min="38" max="39" width="15.1640625" style="3" customWidth="1"/>
-    <col min="40" max="16384" width="8.83203125" style="49"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" s="3" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -5214,16 +5239,16 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>1134</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>1135</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>3</v>
@@ -5232,13 +5257,13 @@
         <v>4</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>1136</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>1137</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>1138</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>648</v>
@@ -5256,22 +5281,22 @@
         <v>8</v>
       </c>
       <c r="R1" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="S1" s="4" t="s">
         <v>1139</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>1140</v>
       </c>
       <c r="T1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="X1" s="3" t="s">
         <v>657</v>
@@ -5292,16 +5317,16 @@
         <v>658</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="AE1" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="AF1" s="3" t="s">
         <v>1231</v>
       </c>
-      <c r="AF1" s="3" t="s">
-        <v>1232</v>
-      </c>
       <c r="AG1" s="3" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="AH1" s="3" t="s">
         <v>686</v>
@@ -5313,18 +5338,18 @@
         <v>712</v>
       </c>
       <c r="AK1" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AL1" s="3" t="s">
         <v>1144</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>1145</v>
-      </c>
-      <c r="AM1" s="3" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="2" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>10</v>
@@ -5378,7 +5403,7 @@
     </row>
     <row r="3" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>12</v>
@@ -5451,7 +5476,7 @@
     </row>
     <row r="4" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>20</v>
@@ -5512,7 +5537,7 @@
       <c r="AB4" s="7"/>
       <c r="AC4" s="3"/>
       <c r="AD4" s="12" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="AE4" s="2"/>
       <c r="AF4" s="2"/>
@@ -5534,7 +5559,7 @@
     </row>
     <row r="5" spans="1:39" s="9" customFormat="1" ht="152" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>26</v>
@@ -5595,7 +5620,7 @@
       <c r="AB5" s="7"/>
       <c r="AC5" s="3"/>
       <c r="AD5" s="12" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="AE5" s="12"/>
       <c r="AF5" s="12"/>
@@ -5621,7 +5646,7 @@
     </row>
     <row r="6" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>30</v>
@@ -5674,7 +5699,7 @@
     </row>
     <row r="7" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>31</v>
@@ -5747,7 +5772,7 @@
         <v>656</v>
       </c>
       <c r="AD7" s="12" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="AE7" s="12"/>
       <c r="AF7" s="12"/>
@@ -5771,7 +5796,7 @@
     </row>
     <row r="8" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>740</v>
@@ -5826,7 +5851,7 @@
     </row>
     <row r="9" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>36</v>
@@ -5879,7 +5904,7 @@
     </row>
     <row r="10" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>37</v>
@@ -5889,7 +5914,7 @@
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>28</v>
@@ -5938,7 +5963,7 @@
       <c r="AB10" s="7"/>
       <c r="AC10" s="3"/>
       <c r="AD10" s="12" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="AE10" s="12"/>
       <c r="AF10" s="12"/>
@@ -5962,7 +5987,7 @@
     </row>
     <row r="11" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>114</v>
@@ -6015,7 +6040,7 @@
     </row>
     <row r="12" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>39</v>
@@ -6068,7 +6093,7 @@
     </row>
     <row r="13" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>40</v>
@@ -6121,7 +6146,7 @@
     </row>
     <row r="14" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>41</v>
@@ -6202,7 +6227,7 @@
     </row>
     <row r="15" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>44</v>
@@ -6275,7 +6300,7 @@
     </row>
     <row r="16" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>47</v>
@@ -6328,7 +6353,7 @@
     </row>
     <row r="17" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>48</v>
@@ -6403,7 +6428,7 @@
     </row>
     <row r="18" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>50</v>
@@ -6456,7 +6481,7 @@
     </row>
     <row r="19" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>51</v>
@@ -6517,7 +6542,7 @@
       <c r="AB19" s="7"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="12" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="AE19" s="12"/>
       <c r="AF19" s="12"/>
@@ -6538,7 +6563,7 @@
     </row>
     <row r="20" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>53</v>
@@ -6591,7 +6616,7 @@
     </row>
     <row r="21" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>54</v>
@@ -6612,11 +6637,15 @@
       <c r="H21" s="8">
         <v>10</v>
       </c>
-      <c r="I21" s="8"/>
+      <c r="I21" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="J21" s="7"/>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
+      <c r="M21" s="8">
+        <v>0.8</v>
+      </c>
       <c r="N21" s="8" t="s">
         <v>17</v>
       </c>
@@ -6643,7 +6672,9 @@
       </c>
       <c r="V21" s="2"/>
       <c r="W21" s="10"/>
-      <c r="X21" s="3"/>
+      <c r="X21" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="Y21" s="7"/>
       <c r="Z21" s="7"/>
       <c r="AA21" s="7"/>
@@ -6666,7 +6697,7 @@
     </row>
     <row r="22" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>58</v>
@@ -6719,7 +6750,7 @@
     </row>
     <row r="23" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>59</v>
@@ -6796,7 +6827,7 @@
     </row>
     <row r="24" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>61</v>
@@ -6879,7 +6910,7 @@
     </row>
     <row r="25" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>64</v>
@@ -6888,7 +6919,7 @@
         <v>65</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
@@ -6934,7 +6965,7 @@
     </row>
     <row r="26" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>66</v>
@@ -6987,7 +7018,7 @@
     </row>
     <row r="27" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>67</v>
@@ -7070,7 +7101,7 @@
     </row>
     <row r="28" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>72</v>
@@ -7123,7 +7154,7 @@
     </row>
     <row r="29" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>73</v>
@@ -7171,7 +7202,7 @@
       <c r="AI29" s="3"/>
       <c r="AJ29" s="3"/>
       <c r="AK29" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>654</v>
@@ -7182,7 +7213,7 @@
     </row>
     <row r="30" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>75</v>
@@ -7237,7 +7268,7 @@
     </row>
     <row r="31" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>77</v>
@@ -7290,7 +7321,7 @@
     </row>
     <row r="32" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>78</v>
@@ -7343,7 +7374,7 @@
     </row>
     <row r="33" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>79</v>
@@ -7418,7 +7449,7 @@
     </row>
     <row r="34" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>82</v>
@@ -7471,7 +7502,7 @@
     </row>
     <row r="35" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>83</v>
@@ -7524,7 +7555,7 @@
     </row>
     <row r="36" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>84</v>
@@ -7577,7 +7608,7 @@
     </row>
     <row r="37" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>85</v>
@@ -7594,11 +7625,15 @@
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
+      <c r="I37" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="J37" s="7"/>
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
+      <c r="M37" s="8">
+        <v>15</v>
+      </c>
       <c r="N37" s="8"/>
       <c r="O37" s="7"/>
       <c r="P37" s="8"/>
@@ -7636,7 +7671,7 @@
     </row>
     <row r="38" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>87</v>
@@ -7695,7 +7730,7 @@
     </row>
     <row r="39" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>90</v>
@@ -7748,7 +7783,7 @@
     </row>
     <row r="40" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>91</v>
@@ -7758,7 +7793,7 @@
       </c>
       <c r="D40" s="7"/>
       <c r="E40" s="7" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>28</v>
@@ -7800,7 +7835,7 @@
       </c>
       <c r="V40" s="2"/>
       <c r="W40" s="17" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="X40" s="3" t="s">
         <v>656</v>
@@ -7815,7 +7850,7 @@
         <v>656</v>
       </c>
       <c r="AD40" s="12" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="AE40" s="12"/>
       <c r="AF40" s="12"/>
@@ -7841,7 +7876,7 @@
     </row>
     <row r="41" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>93</v>
@@ -7894,7 +7929,7 @@
     </row>
     <row r="42" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>94</v>
@@ -7965,7 +8000,7 @@
       <c r="AB42" s="7"/>
       <c r="AC42" s="3"/>
       <c r="AD42" s="12" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="AE42" s="12"/>
       <c r="AF42" s="12"/>
@@ -7990,7 +8025,7 @@
     </row>
     <row r="43" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>98</v>
@@ -8045,7 +8080,7 @@
     </row>
     <row r="44" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>100</v>
@@ -8087,7 +8122,7 @@
       <c r="AI44" s="3"/>
       <c r="AJ44" s="3"/>
       <c r="AK44" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="AL44" s="3" t="s">
         <v>654</v>
@@ -8098,7 +8133,7 @@
     </row>
     <row r="45" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>101</v>
@@ -8167,7 +8202,7 @@
       <c r="AB45" s="7"/>
       <c r="AC45" s="3"/>
       <c r="AD45" s="12" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="AE45" s="12"/>
       <c r="AF45" s="12"/>
@@ -8193,7 +8228,7 @@
     </row>
     <row r="46" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>105</v>
@@ -8246,7 +8281,7 @@
     </row>
     <row r="47" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>106</v>
@@ -8299,7 +8334,7 @@
     </row>
     <row r="48" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>107</v>
@@ -8362,7 +8397,7 @@
     </row>
     <row r="49" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>110</v>
@@ -8429,7 +8464,7 @@
       <c r="AB49" s="7"/>
       <c r="AC49" s="3"/>
       <c r="AD49" s="12" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="AE49" s="12"/>
       <c r="AF49" s="12"/>
@@ -8453,7 +8488,7 @@
     </row>
     <row r="50" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>113</v>
@@ -8506,7 +8541,7 @@
     </row>
     <row r="51" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>115</v>
@@ -8559,7 +8594,7 @@
     </row>
     <row r="52" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>116</v>
@@ -8612,7 +8647,7 @@
     </row>
     <row r="53" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>117</v>
@@ -8697,7 +8732,7 @@
     </row>
     <row r="54" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>120</v>
@@ -8721,9 +8756,7 @@
       <c r="I54" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="J54" s="7" t="s">
-        <v>416</v>
-      </c>
+      <c r="J54" s="7"/>
       <c r="K54" s="8"/>
       <c r="L54" s="8"/>
       <c r="M54" s="8">
@@ -8778,7 +8811,7 @@
     </row>
     <row r="55" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>123</v>
@@ -8831,7 +8864,7 @@
     </row>
     <row r="56" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>124</v>
@@ -8884,7 +8917,7 @@
     </row>
     <row r="57" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>125</v>
@@ -8937,7 +8970,7 @@
     </row>
     <row r="58" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>126</v>
@@ -8990,7 +9023,7 @@
     </row>
     <row r="59" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>127</v>
@@ -9043,7 +9076,7 @@
     </row>
     <row r="60" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>128</v>
@@ -9102,7 +9135,7 @@
       <c r="AB60" s="7"/>
       <c r="AC60" s="3"/>
       <c r="AD60" s="12" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="AE60" s="12" t="s">
         <v>33</v>
@@ -9128,7 +9161,7 @@
     </row>
     <row r="61" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>131</v>
@@ -9193,7 +9226,7 @@
       <c r="AB61" s="7"/>
       <c r="AC61" s="3"/>
       <c r="AD61" s="12" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="AE61" s="12"/>
       <c r="AF61" s="12"/>
@@ -9219,7 +9252,7 @@
     </row>
     <row r="62" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>135</v>
@@ -9272,7 +9305,7 @@
     </row>
     <row r="63" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>136</v>
@@ -9351,7 +9384,7 @@
     </row>
     <row r="64" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>138</v>
@@ -9436,7 +9469,7 @@
     </row>
     <row r="65" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>140</v>
@@ -9489,7 +9522,7 @@
     </row>
     <row r="66" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>141</v>
@@ -9542,7 +9575,7 @@
     </row>
     <row r="67" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>142</v>
@@ -9595,7 +9628,7 @@
     </row>
     <row r="68" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>143</v>
@@ -9648,7 +9681,7 @@
     </row>
     <row r="69" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>144</v>
@@ -9701,7 +9734,7 @@
     </row>
     <row r="70" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>145</v>
@@ -9770,7 +9803,7 @@
     </row>
     <row r="71" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>147</v>
@@ -9823,7 +9856,7 @@
     </row>
     <row r="72" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>148</v>
@@ -9876,7 +9909,7 @@
     </row>
     <row r="73" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>149</v>
@@ -9929,7 +9962,7 @@
     </row>
     <row r="74" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>150</v>
@@ -9982,7 +10015,7 @@
     </row>
     <row r="75" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>151</v>
@@ -10053,7 +10086,7 @@
         <v>656</v>
       </c>
       <c r="AD75" s="12" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AE75" s="12"/>
       <c r="AF75" s="12"/>
@@ -10079,7 +10112,7 @@
     </row>
     <row r="76" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>155</v>
@@ -10132,7 +10165,7 @@
     </row>
     <row r="77" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>156</v>
@@ -10193,7 +10226,7 @@
         <v>656</v>
       </c>
       <c r="AD77" s="12" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="AE77" s="12" t="s">
         <v>33</v>
@@ -10221,7 +10254,7 @@
     </row>
     <row r="78" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>158</v>
@@ -10288,7 +10321,7 @@
     </row>
     <row r="79" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>161</v>
@@ -10341,7 +10374,7 @@
     </row>
     <row r="80" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>162</v>
@@ -10402,7 +10435,7 @@
     </row>
     <row r="81" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>164</v>
@@ -10423,11 +10456,15 @@
       <c r="H81" s="8">
         <v>13</v>
       </c>
-      <c r="I81" s="8"/>
+      <c r="I81" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="J81" s="7"/>
       <c r="K81" s="8"/>
       <c r="L81" s="8"/>
-      <c r="M81" s="8"/>
+      <c r="M81" s="8">
+        <v>0.17</v>
+      </c>
       <c r="N81" s="8"/>
       <c r="O81" s="8"/>
       <c r="P81" s="8">
@@ -10469,7 +10506,7 @@
     </row>
     <row r="82" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>167</v>
@@ -10532,7 +10569,7 @@
       <c r="AB82" s="7"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="12" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="AE82" s="12"/>
       <c r="AF82" s="12"/>
@@ -10557,7 +10594,7 @@
     </row>
     <row r="83" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>171</v>
@@ -10626,7 +10663,7 @@
         <v>656</v>
       </c>
       <c r="AD83" s="12" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="AE83" s="12"/>
       <c r="AF83" s="12"/>
@@ -10652,7 +10689,7 @@
     </row>
     <row r="84" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>173</v>
@@ -10705,7 +10742,7 @@
     </row>
     <row r="85" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>174</v>
@@ -10758,7 +10795,7 @@
     </row>
     <row r="86" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>175</v>
@@ -10821,7 +10858,7 @@
         <v>656</v>
       </c>
       <c r="AD86" s="12" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="AE86" s="12" t="s">
         <v>33</v>
@@ -10849,7 +10886,7 @@
     </row>
     <row r="87" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>177</v>
@@ -10902,7 +10939,7 @@
     </row>
     <row r="88" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>178</v>
@@ -10955,7 +10992,7 @@
     </row>
     <row r="89" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>179</v>
@@ -11008,7 +11045,7 @@
     </row>
     <row r="90" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>180</v>
@@ -11071,7 +11108,7 @@
         <v>656</v>
       </c>
       <c r="AD90" s="12" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="AE90" s="12" t="s">
         <v>33</v>
@@ -11099,7 +11136,7 @@
     </row>
     <row r="91" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>182</v>
@@ -11152,7 +11189,7 @@
     </row>
     <row r="92" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>183</v>
@@ -11207,7 +11244,7 @@
     </row>
     <row r="93" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>185</v>
@@ -11268,7 +11305,7 @@
       <c r="AB93" s="7"/>
       <c r="AC93" s="3"/>
       <c r="AD93" s="12" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="AE93" s="12"/>
       <c r="AF93" s="12"/>
@@ -11294,7 +11331,7 @@
     </row>
     <row r="94" spans="1:39" s="9" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>188</v>
@@ -11353,10 +11390,10 @@
       <c r="AB94" s="7"/>
       <c r="AC94" s="3"/>
       <c r="AD94" s="12" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="AE94" s="12" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="AF94" s="12">
         <v>1</v>
@@ -11383,7 +11420,7 @@
     </row>
     <row r="95" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>191</v>
@@ -11462,7 +11499,7 @@
     </row>
     <row r="96" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>194</v>
@@ -11520,7 +11557,7 @@
       </c>
       <c r="V96" s="3"/>
       <c r="W96" s="10" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="X96" s="3" t="s">
         <v>656</v>
@@ -11533,7 +11570,7 @@
         <v>656</v>
       </c>
       <c r="AD96" s="12" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="AE96" s="12"/>
       <c r="AF96" s="12"/>
@@ -11559,7 +11596,7 @@
     </row>
     <row r="97" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>197</v>
@@ -11618,10 +11655,10 @@
       <c r="AB97" s="7"/>
       <c r="AC97" s="3"/>
       <c r="AD97" s="12" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="AE97" s="12" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="AF97" s="12"/>
       <c r="AG97" s="10" t="s">
@@ -11646,7 +11683,7 @@
     </row>
     <row r="98" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>199</v>
@@ -11699,7 +11736,7 @@
     </row>
     <row r="99" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>200</v>
@@ -11727,7 +11764,7 @@
       <c r="K99" s="8"/>
       <c r="L99" s="8"/>
       <c r="M99" s="8">
-        <v>0.05</v>
+        <v>5</v>
       </c>
       <c r="N99" s="8" t="s">
         <v>17</v>
@@ -11778,7 +11815,7 @@
     </row>
     <row r="100" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B100" s="7" t="s">
         <v>203</v>
@@ -11843,7 +11880,7 @@
     </row>
     <row r="101" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>206</v>
@@ -11896,23 +11933,23 @@
     </row>
     <row r="102" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="22" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D102" s="7"/>
       <c r="E102" s="23" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="F102" s="24" t="s">
         <v>15</v>
       </c>
       <c r="G102" s="24" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H102" s="8">
         <v>66</v>
@@ -11924,10 +11961,10 @@
       <c r="K102" s="8"/>
       <c r="L102" s="8"/>
       <c r="M102" s="8" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="N102" s="8" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="O102" s="8"/>
       <c r="P102" s="8"/>
@@ -11964,7 +12001,7 @@
       </c>
       <c r="AJ102" s="3"/>
       <c r="AK102" s="26" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="AL102" s="3" t="s">
         <v>654</v>
@@ -11975,7 +12012,7 @@
     </row>
     <row r="103" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>207</v>
@@ -12028,7 +12065,7 @@
     </row>
     <row r="104" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>208</v>
@@ -12095,7 +12132,7 @@
       <c r="AB104" s="7"/>
       <c r="AC104" s="3"/>
       <c r="AD104" s="12" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="AE104" s="12"/>
       <c r="AF104" s="12"/>
@@ -12119,7 +12156,7 @@
     </row>
     <row r="105" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>212</v>
@@ -12172,7 +12209,7 @@
     </row>
     <row r="106" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>213</v>
@@ -12241,7 +12278,7 @@
     </row>
     <row r="107" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>215</v>
@@ -12312,7 +12349,7 @@
     </row>
     <row r="108" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>218</v>
@@ -12365,7 +12402,7 @@
     </row>
     <row r="109" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>219</v>
@@ -12418,7 +12455,7 @@
     </row>
     <row r="110" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>220</v>
@@ -12471,7 +12508,7 @@
     </row>
     <row r="111" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>221</v>
@@ -12524,7 +12561,7 @@
     </row>
     <row r="112" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>222</v>
@@ -12577,7 +12614,7 @@
     </row>
     <row r="113" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>223</v>
@@ -12630,7 +12667,7 @@
     </row>
     <row r="114" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>224</v>
@@ -12683,7 +12720,7 @@
     </row>
     <row r="115" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>225</v>
@@ -12756,7 +12793,7 @@
     </row>
     <row r="116" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>228</v>
@@ -12809,7 +12846,7 @@
     </row>
     <row r="117" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>229</v>
@@ -12862,7 +12899,7 @@
     </row>
     <row r="118" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>230</v>
@@ -12915,7 +12952,7 @@
     </row>
     <row r="119" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>231</v>
@@ -12968,7 +13005,7 @@
     </row>
     <row r="120" spans="1:39" s="9" customFormat="1" ht="89" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>232</v>
@@ -13023,7 +13060,7 @@
     </row>
     <row r="121" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>233</v>
@@ -13076,7 +13113,7 @@
     </row>
     <row r="122" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>234</v>
@@ -13129,7 +13166,7 @@
     </row>
     <row r="123" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>235</v>
@@ -13182,7 +13219,7 @@
     </row>
     <row r="124" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>236</v>
@@ -13203,11 +13240,15 @@
       <c r="H124" s="8">
         <v>10</v>
       </c>
-      <c r="I124" s="8"/>
+      <c r="I124" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="J124" s="7"/>
       <c r="K124" s="8"/>
       <c r="L124" s="8"/>
-      <c r="M124" s="8"/>
+      <c r="M124" s="8">
+        <v>1</v>
+      </c>
       <c r="N124" s="8" t="s">
         <v>693</v>
       </c>
@@ -13251,7 +13292,7 @@
     </row>
     <row r="125" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>239</v>
@@ -13304,7 +13345,7 @@
     </row>
     <row r="126" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>240</v>
@@ -13385,7 +13426,7 @@
     </row>
     <row r="127" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>242</v>
@@ -13438,7 +13479,7 @@
     </row>
     <row r="128" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>243</v>
@@ -13499,7 +13540,7 @@
       <c r="AB128" s="7"/>
       <c r="AC128" s="3"/>
       <c r="AD128" s="12" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AE128" s="12"/>
       <c r="AF128" s="12"/>
@@ -13525,7 +13566,7 @@
     </row>
     <row r="129" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>246</v>
@@ -13578,7 +13619,7 @@
     </row>
     <row r="130" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>247</v>
@@ -13633,7 +13674,7 @@
     </row>
     <row r="131" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>248</v>
@@ -13698,7 +13739,7 @@
     </row>
     <row r="132" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>250</v>
@@ -13751,7 +13792,7 @@
     </row>
     <row r="133" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>251</v>
@@ -13826,7 +13867,7 @@
         <v>656</v>
       </c>
       <c r="AD133" s="12" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="AE133" s="12"/>
       <c r="AF133" s="12"/>
@@ -13850,7 +13891,7 @@
     </row>
     <row r="134" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>254</v>
@@ -13903,7 +13944,7 @@
     </row>
     <row r="135" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>255</v>
@@ -13974,7 +14015,7 @@
     </row>
     <row r="136" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>257</v>
@@ -14041,7 +14082,7 @@
         <v>656</v>
       </c>
       <c r="AD136" s="12" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="AE136" s="12"/>
       <c r="AF136" s="12"/>
@@ -14067,7 +14108,7 @@
     </row>
     <row r="137" spans="1:39" s="9" customFormat="1" ht="199" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>258</v>
@@ -14124,7 +14165,7 @@
     </row>
     <row r="138" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>259</v>
@@ -14185,7 +14226,7 @@
         <v>656</v>
       </c>
       <c r="AD138" s="12" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="AE138" s="12" t="s">
         <v>33</v>
@@ -14213,7 +14254,7 @@
     </row>
     <row r="139" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>262</v>
@@ -14267,7 +14308,7 @@
       </c>
       <c r="V139" s="3"/>
       <c r="W139" s="10" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="X139" s="3" t="s">
         <v>656</v>
@@ -14280,7 +14321,7 @@
         <v>656</v>
       </c>
       <c r="AD139" s="12" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="AE139" s="12"/>
       <c r="AF139" s="12"/>
@@ -14306,7 +14347,7 @@
     </row>
     <row r="140" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>264</v>
@@ -14359,7 +14400,7 @@
     </row>
     <row r="141" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>265</v>
@@ -14440,7 +14481,7 @@
     </row>
     <row r="142" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>267</v>
@@ -14493,7 +14534,7 @@
     </row>
     <row r="143" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>268</v>
@@ -14546,7 +14587,7 @@
     </row>
     <row r="144" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>269</v>
@@ -14556,7 +14597,7 @@
       </c>
       <c r="D144" s="7"/>
       <c r="E144" s="7" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="F144" s="7" t="s">
         <v>15</v>
@@ -14605,7 +14646,7 @@
       <c r="AB144" s="7"/>
       <c r="AC144" s="3"/>
       <c r="AD144" s="12" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="AE144" s="12"/>
       <c r="AF144" s="12"/>
@@ -14627,7 +14668,7 @@
     </row>
     <row r="145" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>271</v>
@@ -14680,7 +14721,7 @@
     </row>
     <row r="146" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>272</v>
@@ -14753,7 +14794,7 @@
     </row>
     <row r="147" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>276</v>
@@ -14834,7 +14875,7 @@
     </row>
     <row r="148" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>279</v>
@@ -14887,7 +14928,7 @@
     </row>
     <row r="149" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>280</v>
@@ -14952,7 +14993,7 @@
     </row>
     <row r="150" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>282</v>
@@ -15007,7 +15048,7 @@
     </row>
     <row r="151" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>283</v>
@@ -15060,7 +15101,7 @@
     </row>
     <row r="152" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>284</v>
@@ -15113,7 +15154,7 @@
     </row>
     <row r="153" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>285</v>
@@ -15168,7 +15209,7 @@
     </row>
     <row r="154" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>286</v>
@@ -15239,7 +15280,7 @@
     </row>
     <row r="155" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>289</v>
@@ -15294,7 +15335,7 @@
     </row>
     <row r="156" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>290</v>
@@ -15363,7 +15404,7 @@
     </row>
     <row r="157" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>292</v>
@@ -15426,7 +15467,7 @@
         <v>656</v>
       </c>
       <c r="AD157" s="12" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="AE157" s="12"/>
       <c r="AF157" s="12"/>
@@ -15452,7 +15493,7 @@
     </row>
     <row r="158" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>293</v>
@@ -15505,7 +15546,7 @@
     </row>
     <row r="159" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>294</v>
@@ -15584,7 +15625,7 @@
     </row>
     <row r="160" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>297</v>
@@ -15637,7 +15678,7 @@
     </row>
     <row r="161" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>298</v>
@@ -15702,7 +15743,7 @@
       <c r="AB161" s="7"/>
       <c r="AC161" s="3"/>
       <c r="AD161" s="12" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="AE161" s="12"/>
       <c r="AF161" s="12"/>
@@ -15728,7 +15769,7 @@
     </row>
     <row r="162" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>301</v>
@@ -15797,7 +15838,7 @@
     </row>
     <row r="163" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>304</v>
@@ -15850,7 +15891,7 @@
     </row>
     <row r="164" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>305</v>
@@ -15921,7 +15962,7 @@
         <v>656</v>
       </c>
       <c r="AD164" s="12" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="AE164" s="12"/>
       <c r="AF164" s="12"/>
@@ -15947,7 +15988,7 @@
     </row>
     <row r="165" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>308</v>
@@ -15957,7 +15998,7 @@
       </c>
       <c r="D165" s="7"/>
       <c r="E165" s="7" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="F165" s="7" t="s">
         <v>15</v>
@@ -16012,7 +16053,7 @@
       <c r="AB165" s="7"/>
       <c r="AC165" s="3"/>
       <c r="AD165" s="29" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="AE165" s="29"/>
       <c r="AF165" s="12"/>
@@ -16038,7 +16079,7 @@
     </row>
     <row r="166" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>310</v>
@@ -16091,7 +16132,7 @@
     </row>
     <row r="167" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>311</v>
@@ -16158,7 +16199,7 @@
         <v>656</v>
       </c>
       <c r="AD167" s="12" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="AE167" s="12"/>
       <c r="AF167" s="12"/>
@@ -16184,7 +16225,7 @@
     </row>
     <row r="168" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B168" s="7" t="s">
         <v>313</v>
@@ -16237,7 +16278,7 @@
     </row>
     <row r="169" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B169" s="7" t="s">
         <v>314</v>
@@ -16267,7 +16308,7 @@
       <c r="K169" s="8"/>
       <c r="L169" s="8"/>
       <c r="M169" s="8">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="N169" s="8" t="s">
         <v>122</v>
@@ -16310,7 +16351,7 @@
         <v>656</v>
       </c>
       <c r="AD169" s="12" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="AE169" s="12"/>
       <c r="AF169" s="12"/>
@@ -16334,7 +16375,7 @@
     </row>
     <row r="170" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B170" s="7" t="s">
         <v>317</v>
@@ -16409,7 +16450,7 @@
     </row>
     <row r="171" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B171" s="7" t="s">
         <v>320</v>
@@ -16462,7 +16503,7 @@
     </row>
     <row r="172" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B172" s="7" t="s">
         <v>321</v>
@@ -16515,7 +16556,7 @@
     </row>
     <row r="173" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B173" s="7" t="s">
         <v>322</v>
@@ -16568,7 +16609,7 @@
     </row>
     <row r="174" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B174" s="7" t="s">
         <v>323</v>
@@ -16621,7 +16662,7 @@
     </row>
     <row r="175" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B175" s="7" t="s">
         <v>324</v>
@@ -16704,7 +16745,7 @@
     </row>
     <row r="176" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B176" s="7" t="s">
         <v>327</v>
@@ -16757,7 +16798,7 @@
     </row>
     <row r="177" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B177" s="7" t="s">
         <v>328</v>
@@ -16826,7 +16867,7 @@
     </row>
     <row r="178" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>329</v>
@@ -16891,7 +16932,7 @@
       <c r="AB178" s="7"/>
       <c r="AC178" s="3"/>
       <c r="AD178" s="12" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="AE178" s="12"/>
       <c r="AF178" s="12"/>
@@ -16915,7 +16956,7 @@
     </row>
     <row r="179" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B179" s="7" t="s">
         <v>331</v>
@@ -16968,7 +17009,7 @@
     </row>
     <row r="180" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B180" s="7" t="s">
         <v>332</v>
@@ -17033,7 +17074,7 @@
       <c r="AB180" s="7"/>
       <c r="AC180" s="3"/>
       <c r="AD180" s="30" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="AE180" s="12"/>
       <c r="AF180" s="12"/>
@@ -17057,7 +17098,7 @@
     </row>
     <row r="181" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B181" s="7" t="s">
         <v>335</v>
@@ -17128,7 +17169,7 @@
     </row>
     <row r="182" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B182" s="7" t="s">
         <v>338</v>
@@ -17189,7 +17230,7 @@
       <c r="AB182" s="7"/>
       <c r="AC182" s="3"/>
       <c r="AD182" s="12" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="AE182" s="12"/>
       <c r="AF182" s="12"/>
@@ -17211,7 +17252,7 @@
     </row>
     <row r="183" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B183" s="7" t="s">
         <v>342</v>
@@ -17264,7 +17305,7 @@
     </row>
     <row r="184" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B184" s="7" t="s">
         <v>343</v>
@@ -17317,7 +17358,7 @@
     </row>
     <row r="185" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B185" s="7" t="s">
         <v>344</v>
@@ -17374,7 +17415,7 @@
         <v>656</v>
       </c>
       <c r="AD185" s="12" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="AE185" s="12" t="s">
         <v>33</v>
@@ -17402,7 +17443,7 @@
     </row>
     <row r="186" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B186" s="7" t="s">
         <v>346</v>
@@ -17481,7 +17522,7 @@
     </row>
     <row r="187" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B187" s="7" t="s">
         <v>350</v>
@@ -17534,7 +17575,7 @@
     </row>
     <row r="188" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B188" s="7" t="s">
         <v>351</v>
@@ -17595,10 +17636,10 @@
       <c r="AB188" s="7"/>
       <c r="AC188" s="2"/>
       <c r="AD188" s="12" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="AE188" s="12" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="AF188" s="12"/>
       <c r="AG188" s="10" t="s">
@@ -17623,7 +17664,7 @@
     </row>
     <row r="189" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>353</v>
@@ -17676,7 +17717,7 @@
     </row>
     <row r="190" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B190" s="7" t="s">
         <v>354</v>
@@ -17729,7 +17770,7 @@
     </row>
     <row r="191" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B191" s="7" t="s">
         <v>355</v>
@@ -17788,7 +17829,7 @@
       <c r="AB191" s="7"/>
       <c r="AC191" s="3"/>
       <c r="AD191" s="12" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="AE191" s="12"/>
       <c r="AF191" s="12"/>
@@ -17814,7 +17855,7 @@
     </row>
     <row r="192" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B192" s="7" t="s">
         <v>357</v>
@@ -17867,7 +17908,7 @@
     </row>
     <row r="193" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B193" s="7" t="s">
         <v>358</v>
@@ -17932,10 +17973,10 @@
       <c r="AB193" s="7"/>
       <c r="AC193" s="3"/>
       <c r="AD193" s="12" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="AE193" s="12" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="AF193" s="12"/>
       <c r="AG193" s="10" t="s">
@@ -17957,7 +17998,7 @@
     </row>
     <row r="194" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B194" s="7" t="s">
         <v>361</v>
@@ -18010,7 +18051,7 @@
     </row>
     <row r="195" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B195" s="7" t="s">
         <v>362</v>
@@ -18063,7 +18104,7 @@
     </row>
     <row r="196" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B196" s="7" t="s">
         <v>363</v>
@@ -18132,7 +18173,7 @@
       <c r="AB196" s="7"/>
       <c r="AC196" s="3"/>
       <c r="AD196" s="12" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="AE196" s="12"/>
       <c r="AF196" s="12"/>
@@ -18157,7 +18198,7 @@
     </row>
     <row r="197" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B197" s="7" t="s">
         <v>365</v>
@@ -18212,7 +18253,7 @@
     </row>
     <row r="198" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B198" s="7" t="s">
         <v>366</v>
@@ -18265,7 +18306,7 @@
     </row>
     <row r="199" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B199" s="7" t="s">
         <v>367</v>
@@ -18328,7 +18369,7 @@
       <c r="AB199" s="7"/>
       <c r="AC199" s="3"/>
       <c r="AD199" s="12" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="AE199" s="12"/>
       <c r="AF199" s="12"/>
@@ -18353,7 +18394,7 @@
     </row>
     <row r="200" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>369</v>
@@ -18418,10 +18459,10 @@
       <c r="AB200" s="7"/>
       <c r="AC200" s="3"/>
       <c r="AD200" s="12" t="s">
+        <v>1233</v>
+      </c>
+      <c r="AE200" s="12" t="s">
         <v>1234</v>
-      </c>
-      <c r="AE200" s="12" t="s">
-        <v>1235</v>
       </c>
       <c r="AF200" s="12"/>
       <c r="AG200" s="10" t="s">
@@ -18448,7 +18489,7 @@
     </row>
     <row r="201" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B201" s="7" t="s">
         <v>372</v>
@@ -18501,7 +18542,7 @@
     </row>
     <row r="202" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B202" s="7" t="s">
         <v>373</v>
@@ -18510,7 +18551,7 @@
         <v>71</v>
       </c>
       <c r="D202" s="7" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="E202" s="7"/>
       <c r="F202" s="7"/>
@@ -18556,7 +18597,7 @@
     </row>
     <row r="203" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B203" s="7" t="s">
         <v>374</v>
@@ -18609,7 +18650,7 @@
     </row>
     <row r="204" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B204" s="7" t="s">
         <v>375</v>
@@ -18671,7 +18712,7 @@
         <v>656</v>
       </c>
       <c r="Y204" s="7" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Z204" s="7"/>
       <c r="AA204" s="7"/>
@@ -18680,7 +18721,7 @@
         <v>656</v>
       </c>
       <c r="AD204" s="12" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="AE204" s="12"/>
       <c r="AF204" s="12"/>
@@ -18706,7 +18747,7 @@
     </row>
     <row r="205" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B205" s="7" t="s">
         <v>379</v>
@@ -18763,7 +18804,7 @@
       <c r="AB205" s="7"/>
       <c r="AC205" s="3"/>
       <c r="AD205" s="12" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="AE205" s="12" t="s">
         <v>33</v>
@@ -18791,7 +18832,7 @@
     </row>
     <row r="206" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B206" s="7" t="s">
         <v>382</v>
@@ -18844,7 +18885,7 @@
     </row>
     <row r="207" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B207" s="7" t="s">
         <v>383</v>
@@ -18917,7 +18958,7 @@
     </row>
     <row r="208" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B208" s="7" t="s">
         <v>385</v>
@@ -18970,7 +19011,7 @@
     </row>
     <row r="209" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B209" s="7" t="s">
         <v>386</v>
@@ -19023,7 +19064,7 @@
     </row>
     <row r="210" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B210" s="7" t="s">
         <v>387</v>
@@ -19076,7 +19117,7 @@
     </row>
     <row r="211" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>388</v>
@@ -19129,7 +19170,7 @@
     </row>
     <row r="212" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B212" s="7" t="s">
         <v>389</v>
@@ -19182,7 +19223,7 @@
     </row>
     <row r="213" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B213" s="7" t="s">
         <v>390</v>
@@ -19247,7 +19288,7 @@
         <v>656</v>
       </c>
       <c r="AD213" s="12" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="AE213" s="12"/>
       <c r="AF213" s="12"/>
@@ -19273,7 +19314,7 @@
     </row>
     <row r="214" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B214" s="7" t="s">
         <v>392</v>
@@ -19326,7 +19367,7 @@
     </row>
     <row r="215" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B215" s="7" t="s">
         <v>393</v>
@@ -19405,7 +19446,7 @@
     </row>
     <row r="216" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B216" s="7" t="s">
         <v>395</v>
@@ -19472,7 +19513,7 @@
       <c r="AB216" s="7"/>
       <c r="AC216" s="3"/>
       <c r="AD216" s="12" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="AE216" s="12"/>
       <c r="AF216" s="12"/>
@@ -19498,7 +19539,7 @@
     </row>
     <row r="217" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B217" s="7" t="s">
         <v>397</v>
@@ -19551,7 +19592,7 @@
     </row>
     <row r="218" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B218" s="7" t="s">
         <v>398</v>
@@ -19608,7 +19649,7 @@
       <c r="AB218" s="7"/>
       <c r="AC218" s="3"/>
       <c r="AD218" s="12" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="AE218" s="12" t="s">
         <v>33</v>
@@ -19636,7 +19677,7 @@
     </row>
     <row r="219" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B219" s="7" t="s">
         <v>400</v>
@@ -19689,7 +19730,7 @@
     </row>
     <row r="220" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B220" s="7" t="s">
         <v>401</v>
@@ -19772,7 +19813,7 @@
     </row>
     <row r="221" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B221" s="7" t="s">
         <v>404</v>
@@ -19839,7 +19880,7 @@
         <v>656</v>
       </c>
       <c r="AD221" s="12" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="AE221" s="12"/>
       <c r="AF221" s="12"/>
@@ -19865,7 +19906,7 @@
     </row>
     <row r="222" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>406</v>
@@ -19930,7 +19971,7 @@
       <c r="AB222" s="7"/>
       <c r="AC222" s="2"/>
       <c r="AD222" s="12" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="AE222" s="12"/>
       <c r="AF222" s="12"/>
@@ -19953,7 +19994,7 @@
     </row>
     <row r="223" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B223" s="7" t="s">
         <v>410</v>
@@ -20016,7 +20057,7 @@
       <c r="AB223" s="7"/>
       <c r="AC223" s="3"/>
       <c r="AD223" s="12" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="AE223" s="12"/>
       <c r="AF223" s="12"/>
@@ -20040,7 +20081,7 @@
     </row>
     <row r="224" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B224" s="7" t="s">
         <v>413</v>
@@ -20125,7 +20166,7 @@
     </row>
     <row r="225" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B225" s="7" t="s">
         <v>417</v>
@@ -20212,7 +20253,7 @@
     </row>
     <row r="226" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B226" s="7" t="s">
         <v>419</v>
@@ -20283,7 +20324,7 @@
     </row>
     <row r="227" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B227" s="7" t="s">
         <v>420</v>
@@ -20366,7 +20407,7 @@
     </row>
     <row r="228" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B228" s="7" t="s">
         <v>421</v>
@@ -20419,7 +20460,7 @@
     </row>
     <row r="229" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B229" s="7" t="s">
         <v>422</v>
@@ -20486,7 +20527,7 @@
         <v>656</v>
       </c>
       <c r="AD229" s="12" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="AE229" s="12"/>
       <c r="AF229" s="12"/>
@@ -20512,7 +20553,7 @@
     </row>
     <row r="230" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B230" s="7" t="s">
         <v>423</v>
@@ -20565,7 +20606,7 @@
     </row>
     <row r="231" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B231" s="7" t="s">
         <v>424</v>
@@ -20618,7 +20659,7 @@
     </row>
     <row r="232" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B232" s="32" t="s">
         <v>425</v>
@@ -20683,7 +20724,7 @@
       <c r="AB232" s="32"/>
       <c r="AC232" s="3"/>
       <c r="AD232" s="12" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="AE232" s="12"/>
       <c r="AF232" s="12"/>
@@ -20707,7 +20748,7 @@
     </row>
     <row r="233" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>427</v>
@@ -20762,7 +20803,7 @@
     </row>
     <row r="234" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B234" s="7" t="s">
         <v>428</v>
@@ -20817,7 +20858,7 @@
       <c r="AB234" s="7"/>
       <c r="AC234" s="3"/>
       <c r="AD234" s="12" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="AE234" s="12"/>
       <c r="AF234" s="12"/>
@@ -20837,7 +20878,7 @@
     </row>
     <row r="235" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B235" s="7" t="s">
         <v>431</v>
@@ -20890,7 +20931,7 @@
     </row>
     <row r="236" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B236" s="7" t="s">
         <v>432</v>
@@ -20899,7 +20940,7 @@
         <v>71</v>
       </c>
       <c r="D236" s="7" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="E236" s="7"/>
       <c r="F236" s="7"/>
@@ -20945,7 +20986,7 @@
     </row>
     <row r="237" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B237" s="7" t="s">
         <v>433</v>
@@ -20998,7 +21039,7 @@
     </row>
     <row r="238" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B238" s="7" t="s">
         <v>434</v>
@@ -21053,7 +21094,7 @@
     </row>
     <row r="239" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B239" s="7" t="s">
         <v>435</v>
@@ -21106,7 +21147,7 @@
     </row>
     <row r="240" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B240" s="7" t="s">
         <v>436</v>
@@ -21159,7 +21200,7 @@
     </row>
     <row r="241" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B241" s="7" t="s">
         <v>437</v>
@@ -21214,7 +21255,7 @@
     </row>
     <row r="242" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B242" s="7" t="s">
         <v>438</v>
@@ -21267,7 +21308,7 @@
     </row>
     <row r="243" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B243" s="7" t="s">
         <v>439</v>
@@ -21320,7 +21361,7 @@
     </row>
     <row r="244" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>440</v>
@@ -21373,7 +21414,7 @@
     </row>
     <row r="245" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B245" s="7" t="s">
         <v>441</v>
@@ -21436,7 +21477,7 @@
       <c r="AB245" s="7"/>
       <c r="AC245" s="3"/>
       <c r="AD245" s="12" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="AE245" s="12" t="s">
         <v>33</v>
@@ -21464,7 +21505,7 @@
     </row>
     <row r="246" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B246" s="7" t="s">
         <v>443</v>
@@ -21529,7 +21570,7 @@
       <c r="AB246" s="7"/>
       <c r="AC246" s="3"/>
       <c r="AD246" s="12" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AE246" s="12" t="s">
         <v>33</v>
@@ -21557,7 +21598,7 @@
     </row>
     <row r="247" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B247" s="7" t="s">
         <v>445</v>
@@ -21610,7 +21651,7 @@
     </row>
     <row r="248" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B248" s="7" t="s">
         <v>446</v>
@@ -21663,7 +21704,7 @@
     </row>
     <row r="249" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B249" s="7" t="s">
         <v>447</v>
@@ -21716,7 +21757,7 @@
     </row>
     <row r="250" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B250" s="7" t="s">
         <v>448</v>
@@ -21769,7 +21810,7 @@
     </row>
     <row r="251" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B251" s="7" t="s">
         <v>449</v>
@@ -21822,7 +21863,7 @@
     </row>
     <row r="252" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B252" s="7" t="s">
         <v>450</v>
@@ -21875,7 +21916,7 @@
     </row>
     <row r="253" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B253" s="7" t="s">
         <v>451</v>
@@ -21942,7 +21983,7 @@
     </row>
     <row r="254" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B254" s="7" t="s">
         <v>454</v>
@@ -22015,7 +22056,7 @@
     </row>
     <row r="255" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>457</v>
@@ -22088,7 +22129,7 @@
     </row>
     <row r="256" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B256" s="7" t="s">
         <v>461</v>
@@ -22141,7 +22182,7 @@
     </row>
     <row r="257" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B257" s="7" t="s">
         <v>462</v>
@@ -22194,7 +22235,7 @@
     </row>
     <row r="258" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B258" s="7" t="s">
         <v>463</v>
@@ -22247,7 +22288,7 @@
     </row>
     <row r="259" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B259" s="7" t="s">
         <v>464</v>
@@ -22300,7 +22341,7 @@
     </row>
     <row r="260" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B260" s="7" t="s">
         <v>465</v>
@@ -22353,7 +22394,7 @@
     </row>
     <row r="261" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B261" s="7" t="s">
         <v>466</v>
@@ -22436,7 +22477,7 @@
     </row>
     <row r="262" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B262" s="7" t="s">
         <v>469</v>
@@ -22513,7 +22554,7 @@
         <v>656</v>
       </c>
       <c r="AD262" s="12" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="AE262" s="12"/>
       <c r="AF262" s="12"/>
@@ -22537,7 +22578,7 @@
     </row>
     <row r="263" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B263" s="7" t="s">
         <v>471</v>
@@ -22604,7 +22645,7 @@
         <v>656</v>
       </c>
       <c r="AD263" s="12" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="AE263" s="12"/>
       <c r="AF263" s="12"/>
@@ -22630,7 +22671,7 @@
     </row>
     <row r="264" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B264" s="7" t="s">
         <v>474</v>
@@ -22683,7 +22724,7 @@
     </row>
     <row r="265" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B265" s="7" t="s">
         <v>475</v>
@@ -22740,7 +22781,7 @@
     </row>
     <row r="266" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>476</v>
@@ -22805,7 +22846,7 @@
       <c r="AB266" s="7"/>
       <c r="AC266" s="3"/>
       <c r="AD266" s="12" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="AE266" s="12"/>
       <c r="AF266" s="12"/>
@@ -22829,7 +22870,7 @@
     </row>
     <row r="267" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B267" s="7" t="s">
         <v>479</v>
@@ -22882,7 +22923,7 @@
     </row>
     <row r="268" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B268" s="7" t="s">
         <v>480</v>
@@ -22937,7 +22978,7 @@
     </row>
     <row r="269" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B269" s="7" t="s">
         <v>482</v>
@@ -22996,7 +23037,7 @@
       <c r="AB269" s="7"/>
       <c r="AC269" s="3"/>
       <c r="AD269" s="12" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="AE269" s="12"/>
       <c r="AF269" s="12"/>
@@ -23021,7 +23062,7 @@
     </row>
     <row r="270" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B270" s="7" t="s">
         <v>485</v>
@@ -23074,7 +23115,7 @@
     </row>
     <row r="271" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B271" s="7" t="s">
         <v>486</v>
@@ -23151,7 +23192,7 @@
     </row>
     <row r="272" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B272" s="7" t="s">
         <v>489</v>
@@ -23204,7 +23245,7 @@
     </row>
     <row r="273" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B273" s="7" t="s">
         <v>490</v>
@@ -23257,7 +23298,7 @@
     </row>
     <row r="274" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B274" s="7" t="s">
         <v>491</v>
@@ -23328,7 +23369,7 @@
         <v>28</v>
       </c>
       <c r="AD274" s="12" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="AE274" s="12"/>
       <c r="AF274" s="12"/>
@@ -23354,7 +23395,7 @@
     </row>
     <row r="275" spans="1:39" s="9" customFormat="1" ht="79" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B275" s="7" t="s">
         <v>493</v>
@@ -23421,7 +23462,7 @@
       <c r="AB275" s="7"/>
       <c r="AC275" s="3"/>
       <c r="AD275" s="12" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="AE275" s="12"/>
       <c r="AF275" s="12"/>
@@ -23445,7 +23486,7 @@
     </row>
     <row r="276" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B276" s="7" t="s">
         <v>496</v>
@@ -23502,7 +23543,7 @@
     </row>
     <row r="277" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>497</v>
@@ -23557,7 +23598,7 @@
     </row>
     <row r="278" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="15" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B278" s="7" t="s">
         <v>498</v>
@@ -23709,7 +23750,7 @@
         <v>656</v>
       </c>
       <c r="AD279" s="12" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="AE279" s="11" t="s">
         <v>33</v>
@@ -23736,7 +23777,7 @@
     </row>
     <row r="280" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B280" s="7" t="s">
         <v>503</v>
@@ -23791,7 +23832,7 @@
     </row>
     <row r="281" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B281" s="7" t="s">
         <v>504</v>
@@ -23854,7 +23895,7 @@
         <v>656</v>
       </c>
       <c r="AD281" s="12" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="AE281" s="12" t="s">
         <v>33</v>
@@ -23882,7 +23923,7 @@
     </row>
     <row r="282" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B282" s="7" t="s">
         <v>505</v>
@@ -23935,7 +23976,7 @@
     </row>
     <row r="283" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B283" s="7" t="s">
         <v>506</v>
@@ -24014,7 +24055,7 @@
     </row>
     <row r="284" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B284" s="7" t="s">
         <v>507</v>
@@ -24067,7 +24108,7 @@
     </row>
     <row r="285" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B285" s="7" t="s">
         <v>508</v>
@@ -24108,7 +24149,7 @@
         <v>18</v>
       </c>
       <c r="R285" s="7" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="S285" s="8" t="s">
         <v>19</v>
@@ -24156,7 +24197,7 @@
     </row>
     <row r="286" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B286" s="7" t="s">
         <v>510</v>
@@ -24227,7 +24268,7 @@
         <v>656</v>
       </c>
       <c r="AD286" s="12" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="AE286" s="12"/>
       <c r="AF286" s="12"/>
@@ -24253,7 +24294,7 @@
     </row>
     <row r="287" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B287" s="7" t="s">
         <v>513</v>
@@ -24308,7 +24349,7 @@
     </row>
     <row r="288" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>514</v>
@@ -24381,7 +24422,7 @@
         <v>656</v>
       </c>
       <c r="AD288" s="12" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="AE288" s="12"/>
       <c r="AF288" s="12"/>
@@ -24407,7 +24448,7 @@
     </row>
     <row r="289" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="15" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B289" s="7" t="s">
         <v>517</v>
@@ -24416,7 +24457,7 @@
         <v>88</v>
       </c>
       <c r="D289" s="7" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="E289" s="7"/>
       <c r="F289" s="7"/>
@@ -24464,7 +24505,7 @@
     </row>
     <row r="290" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B290" s="7" t="s">
         <v>518</v>
@@ -24517,7 +24558,7 @@
     </row>
     <row r="291" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B291" s="7" t="s">
         <v>519</v>
@@ -24570,7 +24611,7 @@
     </row>
     <row r="292" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B292" s="7" t="s">
         <v>520</v>
@@ -24631,7 +24672,7 @@
       <c r="AB292" s="7"/>
       <c r="AC292" s="3"/>
       <c r="AD292" s="12" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="AE292" s="12"/>
       <c r="AF292" s="12"/>
@@ -24656,7 +24697,7 @@
     </row>
     <row r="293" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B293" s="7" t="s">
         <v>521</v>
@@ -24717,13 +24758,13 @@
       <c r="AB293" s="7"/>
       <c r="AC293" s="3"/>
       <c r="AD293" s="12" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="AE293" s="12" t="s">
+        <v>1234</v>
+      </c>
+      <c r="AF293" s="12" t="s">
         <v>1235</v>
-      </c>
-      <c r="AF293" s="12" t="s">
-        <v>1236</v>
       </c>
       <c r="AG293" s="10" t="s">
         <v>688</v>
@@ -24745,7 +24786,7 @@
     </row>
     <row r="294" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B294" s="7" t="s">
         <v>524</v>
@@ -24798,7 +24839,7 @@
     </row>
     <row r="295" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B295" s="7" t="s">
         <v>525</v>
@@ -24865,7 +24906,7 @@
         <v>656</v>
       </c>
       <c r="AD295" s="12" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="AE295" s="12" t="s">
         <v>33</v>
@@ -24893,7 +24934,7 @@
     </row>
     <row r="296" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B296" s="7" t="s">
         <v>527</v>
@@ -24976,7 +25017,7 @@
     </row>
     <row r="297" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B297" s="7" t="s">
         <v>529</v>
@@ -25029,7 +25070,7 @@
     </row>
     <row r="298" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B298" s="7" t="s">
         <v>530</v>
@@ -25082,7 +25123,7 @@
     </row>
     <row r="299" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>531</v>
@@ -25155,7 +25196,7 @@
     </row>
     <row r="300" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B300" s="7" t="s">
         <v>533</v>
@@ -25208,7 +25249,7 @@
     </row>
     <row r="301" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B301" s="7" t="s">
         <v>534</v>
@@ -25261,7 +25302,7 @@
     </row>
     <row r="302" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B302" s="7" t="s">
         <v>535</v>
@@ -25328,7 +25369,7 @@
     </row>
     <row r="303" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B303" s="7" t="s">
         <v>537</v>
@@ -25381,7 +25422,7 @@
     </row>
     <row r="304" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B304" s="7" t="s">
         <v>538</v>
@@ -25434,7 +25475,7 @@
     </row>
     <row r="305" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B305" s="7" t="s">
         <v>539</v>
@@ -25503,7 +25544,7 @@
       <c r="AB305" s="7"/>
       <c r="AC305" s="3"/>
       <c r="AD305" s="12" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="AE305" s="12"/>
       <c r="AF305" s="12"/>
@@ -25529,7 +25570,7 @@
     </row>
     <row r="306" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="15" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B306" s="7" t="s">
         <v>542</v>
@@ -25584,7 +25625,7 @@
     </row>
     <row r="307" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B307" s="7" t="s">
         <v>543</v>
@@ -25637,7 +25678,7 @@
     </row>
     <row r="308" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B308" s="7" t="s">
         <v>544</v>
@@ -25692,7 +25733,7 @@
     </row>
     <row r="309" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B309" s="7" t="s">
         <v>545</v>
@@ -25745,49 +25786,89 @@
     </row>
     <row r="310" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="15" t="s">
-        <v>1126</v>
-      </c>
-      <c r="B310" s="7" t="s">
-        <v>310</v>
+        <v>1123</v>
+      </c>
+      <c r="B310" s="37" t="s">
+        <v>1250</v>
       </c>
       <c r="C310" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D310" s="7"/>
+      <c r="E310" s="7" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F310" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G310" s="7" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H310" s="8">
+        <v>12</v>
+      </c>
+      <c r="I310" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J310" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K310" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D310" s="7"/>
-      <c r="E310" s="7"/>
-      <c r="F310" s="7"/>
-      <c r="G310" s="7"/>
-      <c r="H310" s="8"/>
-      <c r="I310" s="8"/>
-      <c r="J310" s="7"/>
-      <c r="K310" s="8"/>
       <c r="L310" s="8"/>
-      <c r="M310" s="8"/>
-      <c r="N310" s="8"/>
-      <c r="O310" s="8"/>
-      <c r="P310" s="8"/>
-      <c r="Q310" s="8"/>
-      <c r="R310" s="7"/>
-      <c r="S310" s="8"/>
+      <c r="M310" s="8" t="s">
+        <v>1253</v>
+      </c>
+      <c r="N310" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="O310" s="8">
+        <v>10</v>
+      </c>
+      <c r="P310" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="Q310" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="R310" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="S310" s="8" t="s">
+        <v>19</v>
+      </c>
       <c r="T310" s="5">
-        <v>18</v>
-      </c>
-      <c r="U310" s="3"/>
-      <c r="V310" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="U310" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="V310" s="3" t="s">
+        <v>656</v>
+      </c>
       <c r="W310" s="10"/>
-      <c r="X310" s="3"/>
+      <c r="X310" s="3" t="s">
+        <v>656</v>
+      </c>
       <c r="Y310" s="7"/>
       <c r="Z310" s="7"/>
       <c r="AA310" s="7"/>
       <c r="AB310" s="7"/>
       <c r="AC310" s="3"/>
-      <c r="AD310" s="11"/>
+      <c r="AD310" s="12" t="s">
+        <v>1255</v>
+      </c>
       <c r="AE310" s="11"/>
       <c r="AF310" s="11"/>
-      <c r="AI310" s="3"/>
-      <c r="AJ310" s="3"/>
+      <c r="AI310" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="AJ310" s="3">
+        <v>9</v>
+      </c>
       <c r="AK310" s="15" t="s">
-        <v>1060</v>
+        <v>1254</v>
       </c>
       <c r="AL310" s="3" t="s">
         <v>654</v>
@@ -25798,7 +25879,7 @@
     </row>
     <row r="311" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="35" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B311" s="7" t="s">
         <v>546</v>
@@ -25861,7 +25942,7 @@
         <v>656</v>
       </c>
       <c r="AD311" s="12" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="AE311" s="12"/>
       <c r="AF311" s="12"/>
@@ -25876,7 +25957,7 @@
         <v>12</v>
       </c>
       <c r="AK311" s="35" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="AL311" s="3" t="s">
         <v>654</v>
@@ -25887,7 +25968,7 @@
     </row>
     <row r="312" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B312" s="7" t="s">
         <v>549</v>
@@ -25931,7 +26012,7 @@
       <c r="AI312" s="3"/>
       <c r="AJ312" s="3"/>
       <c r="AK312" s="15" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="AL312" s="3" t="s">
         <v>654</v>
@@ -25942,7 +26023,7 @@
     </row>
     <row r="313" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="15" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B313" s="7" t="s">
         <v>550</v>
@@ -25995,7 +26076,7 @@
     </row>
     <row r="314" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B314" s="7" t="s">
         <v>551</v>
@@ -26037,7 +26118,7 @@
       <c r="AI314" s="3"/>
       <c r="AJ314" s="3"/>
       <c r="AK314" s="15" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="AL314" s="3" t="s">
         <v>654</v>
@@ -26048,7 +26129,7 @@
     </row>
     <row r="315" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B315" s="7" t="s">
         <v>552</v>
@@ -26092,7 +26173,7 @@
       <c r="AI315" s="3"/>
       <c r="AJ315" s="3"/>
       <c r="AK315" s="15" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="AL315" s="3" t="s">
         <v>654</v>
@@ -26103,7 +26184,7 @@
     </row>
     <row r="316" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B316" s="7" t="s">
         <v>553</v>
@@ -26176,7 +26257,7 @@
       </c>
       <c r="AC316" s="3"/>
       <c r="AD316" s="12" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="AE316" s="12"/>
       <c r="AF316" s="12"/>
@@ -26190,7 +26271,7 @@
         <v>63</v>
       </c>
       <c r="AK316" s="15" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="AL316" s="3" t="s">
         <v>654</v>
@@ -26201,7 +26282,7 @@
     </row>
     <row r="317" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B317" s="7" t="s">
         <v>555</v>
@@ -26243,7 +26324,7 @@
       <c r="AI317" s="3"/>
       <c r="AJ317" s="3"/>
       <c r="AK317" s="15" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="AL317" s="3" t="s">
         <v>654</v>
@@ -26254,7 +26335,7 @@
     </row>
     <row r="318" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B318" s="7" t="s">
         <v>556</v>
@@ -26296,7 +26377,7 @@
       <c r="AI318" s="3"/>
       <c r="AJ318" s="3"/>
       <c r="AK318" s="15" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="AL318" s="3" t="s">
         <v>655</v>
@@ -26307,7 +26388,7 @@
     </row>
     <row r="319" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B319" s="7" t="s">
         <v>557</v>
@@ -26381,7 +26462,7 @@
       </c>
       <c r="AJ319" s="3"/>
       <c r="AK319" s="15" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="AL319" s="3" t="s">
         <v>654</v>
@@ -26392,7 +26473,7 @@
     </row>
     <row r="320" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B320" s="7" t="s">
         <v>559</v>
@@ -26453,7 +26534,7 @@
       <c r="AB320" s="7"/>
       <c r="AC320" s="2"/>
       <c r="AD320" s="12" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="AE320" s="12"/>
       <c r="AF320" s="12"/>
@@ -26467,7 +26548,7 @@
         <v>100</v>
       </c>
       <c r="AK320" s="15" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="AL320" s="3" t="s">
         <v>654</v>
@@ -26478,7 +26559,7 @@
     </row>
     <row r="321" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>561</v>
@@ -26520,7 +26601,7 @@
       <c r="AI321" s="3"/>
       <c r="AJ321" s="3"/>
       <c r="AK321" s="15" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="AL321" s="3" t="s">
         <v>654</v>
@@ -26531,7 +26612,7 @@
     </row>
     <row r="322" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B322" s="7" t="s">
         <v>562</v>
@@ -26573,7 +26654,7 @@
       <c r="AI322" s="3"/>
       <c r="AJ322" s="3"/>
       <c r="AK322" s="15" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="AL322" s="3" t="s">
         <v>654</v>
@@ -26584,7 +26665,7 @@
     </row>
     <row r="323" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="15" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B323" s="7" t="s">
         <v>563</v>
@@ -26658,7 +26739,7 @@
       </c>
       <c r="AJ323" s="3"/>
       <c r="AK323" s="15" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="AL323" s="3" t="s">
         <v>654</v>
@@ -26669,7 +26750,7 @@
     </row>
     <row r="324" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B324" s="7" t="s">
         <v>566</v>
@@ -26711,7 +26792,7 @@
       <c r="AI324" s="3"/>
       <c r="AJ324" s="3"/>
       <c r="AK324" s="15" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="AL324" s="3" t="s">
         <v>654</v>
@@ -26722,7 +26803,7 @@
     </row>
     <row r="325" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B325" s="7" t="s">
         <v>567</v>
@@ -26764,7 +26845,7 @@
       <c r="AI325" s="3"/>
       <c r="AJ325" s="3"/>
       <c r="AK325" s="15" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="AL325" s="3" t="s">
         <v>654</v>
@@ -26775,7 +26856,7 @@
     </row>
     <row r="326" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B326" s="7" t="s">
         <v>568</v>
@@ -26817,7 +26898,7 @@
       <c r="AI326" s="3"/>
       <c r="AJ326" s="3"/>
       <c r="AK326" s="15" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="AL326" s="3" t="s">
         <v>654</v>
@@ -26828,7 +26909,7 @@
     </row>
     <row r="327" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B327" s="7" t="s">
         <v>569</v>
@@ -26872,7 +26953,7 @@
       <c r="AI327" s="3"/>
       <c r="AJ327" s="3"/>
       <c r="AK327" s="15" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="AL327" s="3" t="s">
         <v>654</v>
@@ -26883,7 +26964,7 @@
     </row>
     <row r="328" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B328" s="7" t="s">
         <v>570</v>
@@ -26937,7 +27018,7 @@
       </c>
       <c r="V328" s="3"/>
       <c r="W328" s="10" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="X328" s="3" t="s">
         <v>656</v>
@@ -26950,7 +27031,7 @@
         <v>656</v>
       </c>
       <c r="AD328" s="12" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="AE328" s="12" t="s">
         <v>33</v>
@@ -26969,7 +27050,7 @@
       </c>
       <c r="AJ328" s="3"/>
       <c r="AK328" s="15" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="AL328" s="3" t="s">
         <v>654</v>
@@ -26980,7 +27061,7 @@
     </row>
     <row r="329" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="15" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B329" s="7" t="s">
         <v>573</v>
@@ -27022,7 +27103,7 @@
       <c r="AI329" s="3"/>
       <c r="AJ329" s="3"/>
       <c r="AK329" s="15" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AL329" s="3" t="s">
         <v>654</v>
@@ -27033,7 +27114,7 @@
     </row>
     <row r="330" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B330" s="7" t="s">
         <v>574</v>
@@ -27075,7 +27156,7 @@
       <c r="AI330" s="3"/>
       <c r="AJ330" s="3"/>
       <c r="AK330" s="15" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AL330" s="3" t="s">
         <v>654</v>
@@ -27086,7 +27167,7 @@
     </row>
     <row r="331" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B331" s="7" t="s">
         <v>575</v>
@@ -27128,7 +27209,7 @@
       <c r="AI331" s="3"/>
       <c r="AJ331" s="3"/>
       <c r="AK331" s="15" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="AL331" s="3" t="s">
         <v>654</v>
@@ -27139,7 +27220,7 @@
     </row>
     <row r="332" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="15" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>576</v>
@@ -27204,10 +27285,10 @@
       <c r="AB332" s="7"/>
       <c r="AC332" s="2"/>
       <c r="AD332" s="12" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="AE332" s="12" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="AF332" s="12"/>
       <c r="AG332" s="10" t="s">
@@ -27219,7 +27300,7 @@
       </c>
       <c r="AJ332" s="3"/>
       <c r="AK332" s="15" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="AL332" s="3" t="s">
         <v>654</v>
@@ -27230,7 +27311,7 @@
     </row>
     <row r="333" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B333" s="7" t="s">
         <v>579</v>
@@ -27272,7 +27353,7 @@
       <c r="AI333" s="3"/>
       <c r="AJ333" s="3"/>
       <c r="AK333" s="15" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="AL333" s="3" t="s">
         <v>654</v>
@@ -27283,7 +27364,7 @@
     </row>
     <row r="334" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B334" s="7" t="s">
         <v>580</v>
@@ -27325,7 +27406,7 @@
       <c r="AI334" s="3"/>
       <c r="AJ334" s="3"/>
       <c r="AK334" s="15" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AL334" s="3" t="s">
         <v>654</v>
@@ -27336,7 +27417,7 @@
     </row>
     <row r="335" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="36" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B335" s="37" t="s">
         <v>695</v>
@@ -27378,7 +27459,7 @@
       <c r="AI335" s="3"/>
       <c r="AJ335" s="3"/>
       <c r="AK335" s="36" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="AL335" s="3" t="s">
         <v>654</v>
@@ -27389,7 +27470,7 @@
     </row>
     <row r="336" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="36" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B336" s="37" t="s">
         <v>742</v>
@@ -27462,7 +27543,7 @@
       <c r="AB336" s="7"/>
       <c r="AC336" s="3"/>
       <c r="AD336" s="43" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="AE336" s="43"/>
       <c r="AF336" s="43"/>
@@ -27474,7 +27555,7 @@
       </c>
       <c r="AJ336" s="3"/>
       <c r="AK336" s="36" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="AL336" s="3" t="s">
         <v>654</v>
@@ -27485,7 +27566,7 @@
     </row>
     <row r="337" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="36" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B337" s="37" t="s">
         <v>696</v>
@@ -27526,7 +27607,7 @@
       <c r="AI337" s="3"/>
       <c r="AJ337" s="3"/>
       <c r="AK337" s="36" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="AL337" s="3" t="s">
         <v>654</v>
@@ -27537,7 +27618,7 @@
     </row>
     <row r="338" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="36" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B338" s="37" t="s">
         <v>697</v>
@@ -27578,7 +27659,7 @@
       <c r="AI338" s="3"/>
       <c r="AJ338" s="3"/>
       <c r="AK338" s="36" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="AL338" s="3" t="s">
         <v>654</v>
@@ -27589,7 +27670,7 @@
     </row>
     <row r="339" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="36" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B339" s="37" t="s">
         <v>698</v>
@@ -27646,7 +27727,7 @@
       <c r="AI339" s="3"/>
       <c r="AJ339" s="3"/>
       <c r="AK339" s="36" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="AL339" s="3" t="s">
         <v>654</v>
@@ -27657,7 +27738,7 @@
     </row>
     <row r="340" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="36" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B340" s="37" t="s">
         <v>708</v>
@@ -27699,7 +27780,7 @@
       <c r="AI340" s="3"/>
       <c r="AJ340" s="3"/>
       <c r="AK340" s="46" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="AL340" s="3" t="s">
         <v>654</v>
@@ -27710,7 +27791,7 @@
     </row>
     <row r="341" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="15" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B341" s="7" t="s">
         <v>741</v>
@@ -27762,7 +27843,7 @@
       </c>
       <c r="V341" s="3"/>
       <c r="W341" s="10" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="X341" s="3"/>
       <c r="Y341" s="7"/>
@@ -27773,7 +27854,7 @@
         <v>656</v>
       </c>
       <c r="AD341" s="12" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="AE341" s="12" t="s">
         <v>33</v>
@@ -27803,7 +27884,7 @@
     </row>
     <row r="342" spans="1:39" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B342" s="47" t="s">
         <v>746</v>
@@ -27813,19 +27894,19 @@
       </c>
       <c r="F342" s="48"/>
       <c r="J342" s="48"/>
-      <c r="K342" s="50"/>
-      <c r="L342" s="50"/>
-      <c r="O342" s="50"/>
-      <c r="R342" s="52"/>
+      <c r="K342" s="49"/>
+      <c r="L342" s="49"/>
+      <c r="O342" s="49"/>
+      <c r="R342" s="51"/>
       <c r="T342" s="3">
         <v>31</v>
       </c>
-      <c r="Y342" s="52"/>
-      <c r="Z342" s="52"/>
-      <c r="AA342" s="52"/>
-      <c r="AB342" s="52"/>
-      <c r="AK342" s="53" t="s">
-        <v>1090</v>
+      <c r="Y342" s="51"/>
+      <c r="Z342" s="51"/>
+      <c r="AA342" s="51"/>
+      <c r="AB342" s="51"/>
+      <c r="AK342" s="52" t="s">
+        <v>1089</v>
       </c>
       <c r="AL342" s="3" t="s">
         <v>655</v>
@@ -27836,7 +27917,7 @@
     </row>
     <row r="343" spans="1:39" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B343" s="12" t="s">
         <v>747</v>
@@ -27849,19 +27930,19 @@
       </c>
       <c r="F343" s="48"/>
       <c r="J343" s="48"/>
-      <c r="K343" s="50"/>
-      <c r="L343" s="50"/>
-      <c r="O343" s="50"/>
-      <c r="R343" s="52"/>
+      <c r="K343" s="49"/>
+      <c r="L343" s="49"/>
+      <c r="O343" s="49"/>
+      <c r="R343" s="51"/>
       <c r="T343" s="3">
         <v>52</v>
       </c>
-      <c r="Y343" s="52"/>
-      <c r="Z343" s="52"/>
-      <c r="AA343" s="52"/>
-      <c r="AB343" s="52"/>
+      <c r="Y343" s="51"/>
+      <c r="Z343" s="51"/>
+      <c r="AA343" s="51"/>
+      <c r="AB343" s="51"/>
       <c r="AK343" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="AL343" s="3" t="s">
         <v>654</v>
@@ -27872,7 +27953,7 @@
     </row>
     <row r="344" spans="1:39" s="3" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>749</v>
@@ -27919,7 +28000,7 @@
       <c r="R344" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="S344" s="54" t="s">
+      <c r="S344" s="53" t="s">
         <v>19</v>
       </c>
       <c r="T344" s="3">
@@ -27929,7 +28010,7 @@
         <v>97</v>
       </c>
       <c r="W344" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="X344" s="3" t="s">
         <v>656</v>
@@ -27948,7 +28029,7 @@
         <v>28</v>
       </c>
       <c r="AD344" s="12" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="AE344" s="12"/>
       <c r="AF344" s="12"/>
@@ -27961,8 +28042,8 @@
       <c r="AJ344" s="3">
         <v>24</v>
       </c>
-      <c r="AK344" s="55" t="s">
-        <v>1092</v>
+      <c r="AK344" s="54" t="s">
+        <v>1091</v>
       </c>
       <c r="AL344" s="3" t="s">
         <v>655</v>
@@ -27973,28 +28054,28 @@
     </row>
     <row r="345" spans="1:39" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="38" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B345" s="56" t="s">
-        <v>1094</v>
+        <v>1131</v>
+      </c>
+      <c r="B345" s="55" t="s">
+        <v>1093</v>
       </c>
       <c r="C345" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="D345" s="57" t="s">
-        <v>1100</v>
-      </c>
-      <c r="E345" s="57"/>
+      <c r="D345" s="56" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E345" s="56"/>
       <c r="F345" s="39"/>
       <c r="G345" s="39"/>
       <c r="H345" s="39"/>
       <c r="I345" s="42"/>
       <c r="J345" s="37"/>
-      <c r="K345" s="50"/>
-      <c r="L345" s="50"/>
+      <c r="K345" s="49"/>
+      <c r="L345" s="49"/>
       <c r="M345" s="42"/>
       <c r="N345" s="42"/>
-      <c r="O345" s="50"/>
+      <c r="O345" s="49"/>
       <c r="P345" s="42"/>
       <c r="Q345" s="38"/>
       <c r="R345" s="38"/>
@@ -28002,16 +28083,16 @@
       <c r="T345" s="41">
         <v>28</v>
       </c>
-      <c r="U345" s="58" t="s">
+      <c r="U345" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="V345" s="58"/>
-      <c r="Y345" s="52"/>
-      <c r="Z345" s="52"/>
-      <c r="AA345" s="52"/>
-      <c r="AB345" s="52"/>
-      <c r="AK345" s="59" t="s">
-        <v>1108</v>
+      <c r="V345" s="57"/>
+      <c r="Y345" s="51"/>
+      <c r="Z345" s="51"/>
+      <c r="AA345" s="51"/>
+      <c r="AB345" s="51"/>
+      <c r="AK345" s="58" t="s">
+        <v>1107</v>
       </c>
       <c r="AL345" s="42" t="s">
         <v>654</v>
@@ -28022,10 +28103,10 @@
     </row>
     <row r="346" spans="1:39" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="38" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B346" s="37" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C346" s="38" t="s">
         <v>11</v>
@@ -28037,11 +28118,11 @@
       <c r="H346" s="39"/>
       <c r="I346" s="39"/>
       <c r="J346" s="40"/>
-      <c r="K346" s="50"/>
-      <c r="L346" s="50"/>
+      <c r="K346" s="49"/>
+      <c r="L346" s="49"/>
       <c r="M346" s="39"/>
       <c r="N346" s="39"/>
-      <c r="O346" s="50"/>
+      <c r="O346" s="49"/>
       <c r="P346" s="39"/>
       <c r="Q346" s="39"/>
       <c r="R346" s="40"/>
@@ -28049,16 +28130,16 @@
       <c r="T346" s="41">
         <v>18</v>
       </c>
-      <c r="U346" s="58" t="s">
+      <c r="U346" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="V346" s="58"/>
-      <c r="Y346" s="52"/>
-      <c r="Z346" s="52"/>
-      <c r="AA346" s="52"/>
-      <c r="AB346" s="52"/>
-      <c r="AK346" s="56" t="s">
-        <v>1109</v>
+      <c r="V346" s="57"/>
+      <c r="Y346" s="51"/>
+      <c r="Z346" s="51"/>
+      <c r="AA346" s="51"/>
+      <c r="AB346" s="51"/>
+      <c r="AK346" s="55" t="s">
+        <v>1108</v>
       </c>
       <c r="AL346" s="42" t="s">
         <v>654</v>
@@ -28069,10 +28150,10 @@
     </row>
     <row r="347" spans="1:39" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="38" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B347" s="37" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C347" s="38" t="s">
         <v>11</v>
@@ -28084,11 +28165,11 @@
       <c r="H347" s="39"/>
       <c r="I347" s="39"/>
       <c r="J347" s="40"/>
-      <c r="K347" s="50"/>
-      <c r="L347" s="50"/>
+      <c r="K347" s="49"/>
+      <c r="L347" s="49"/>
       <c r="M347" s="39"/>
       <c r="N347" s="39"/>
-      <c r="O347" s="50"/>
+      <c r="O347" s="49"/>
       <c r="P347" s="39"/>
       <c r="Q347" s="39"/>
       <c r="R347" s="40"/>
@@ -28096,16 +28177,16 @@
       <c r="T347" s="41">
         <v>12</v>
       </c>
-      <c r="U347" s="58" t="s">
+      <c r="U347" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="V347" s="58"/>
-      <c r="Y347" s="52"/>
-      <c r="Z347" s="52"/>
-      <c r="AA347" s="52"/>
-      <c r="AB347" s="52"/>
-      <c r="AK347" s="56" t="s">
-        <v>1110</v>
+      <c r="V347" s="57"/>
+      <c r="Y347" s="51"/>
+      <c r="Z347" s="51"/>
+      <c r="AA347" s="51"/>
+      <c r="AB347" s="51"/>
+      <c r="AK347" s="55" t="s">
+        <v>1109</v>
       </c>
       <c r="AL347" s="42" t="s">
         <v>654</v>
@@ -28116,10 +28197,10 @@
     </row>
     <row r="348" spans="1:39" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="38" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B348" s="37" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C348" s="38" t="s">
         <v>11</v>
@@ -28131,11 +28212,11 @@
       <c r="H348" s="39"/>
       <c r="I348" s="39"/>
       <c r="J348" s="40"/>
-      <c r="K348" s="50"/>
-      <c r="L348" s="50"/>
+      <c r="K348" s="49"/>
+      <c r="L348" s="49"/>
       <c r="M348" s="39"/>
       <c r="N348" s="39"/>
-      <c r="O348" s="50"/>
+      <c r="O348" s="49"/>
       <c r="P348" s="39"/>
       <c r="Q348" s="39"/>
       <c r="R348" s="40"/>
@@ -28143,16 +28224,16 @@
       <c r="T348" s="41">
         <v>23</v>
       </c>
-      <c r="U348" s="58" t="s">
+      <c r="U348" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="V348" s="58"/>
-      <c r="Y348" s="52"/>
-      <c r="Z348" s="52"/>
-      <c r="AA348" s="52"/>
-      <c r="AB348" s="52"/>
-      <c r="AK348" s="60" t="s">
-        <v>1111</v>
+      <c r="V348" s="57"/>
+      <c r="Y348" s="51"/>
+      <c r="Z348" s="51"/>
+      <c r="AA348" s="51"/>
+      <c r="AB348" s="51"/>
+      <c r="AK348" s="59" t="s">
+        <v>1110</v>
       </c>
       <c r="AL348" s="42" t="s">
         <v>654</v>
@@ -28163,17 +28244,17 @@
     </row>
     <row r="349" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="38" t="s">
-        <v>1129</v>
-      </c>
-      <c r="B349" s="61" t="s">
-        <v>1097</v>
-      </c>
-      <c r="C349" s="62" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B349" s="60" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C349" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="D349" s="63"/>
-      <c r="E349" s="64" t="s">
-        <v>1107</v>
+      <c r="D349" s="62"/>
+      <c r="E349" s="63" t="s">
+        <v>1106</v>
       </c>
       <c r="F349" s="9" t="s">
         <v>28</v>
@@ -28181,28 +28262,28 @@
       <c r="H349" s="9">
         <v>27</v>
       </c>
-      <c r="I349" s="65" t="s">
+      <c r="I349" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="J349" s="61" t="s">
+      <c r="J349" s="60" t="s">
         <v>29</v>
       </c>
       <c r="K349" s="8"/>
       <c r="L349" s="8"/>
-      <c r="M349" s="65" t="s">
+      <c r="M349" s="64" t="s">
         <v>668</v>
       </c>
-      <c r="N349" s="65" t="s">
+      <c r="N349" s="64" t="s">
         <v>615</v>
       </c>
       <c r="O349" s="8"/>
-      <c r="P349" s="65" t="s">
-        <v>1105</v>
-      </c>
-      <c r="Q349" s="65" t="s">
+      <c r="P349" s="64" t="s">
+        <v>1104</v>
+      </c>
+      <c r="Q349" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="R349" s="65" t="s">
+      <c r="R349" s="64" t="s">
         <v>71</v>
       </c>
       <c r="S349" s="42" t="s">
@@ -28211,10 +28292,10 @@
       <c r="T349" s="41">
         <v>27</v>
       </c>
-      <c r="U349" s="58" t="s">
+      <c r="U349" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="V349" s="58"/>
+      <c r="V349" s="57"/>
       <c r="W349" s="10"/>
       <c r="X349" s="3" t="s">
         <v>656</v>
@@ -28229,7 +28310,7 @@
         <v>656</v>
       </c>
       <c r="AD349" s="12" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="AE349" s="12" t="s">
         <v>33</v>
@@ -28247,8 +28328,8 @@
       <c r="AJ349" s="3">
         <v>27</v>
       </c>
-      <c r="AK349" s="56" t="s">
-        <v>1112</v>
+      <c r="AK349" s="55" t="s">
+        <v>1111</v>
       </c>
       <c r="AL349" s="42" t="s">
         <v>654</v>
@@ -28259,34 +28340,34 @@
     </row>
     <row r="350" spans="1:39" s="9" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="38" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B350" s="61" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C350" s="62" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B350" s="60" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C350" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="D350" s="61" t="s">
-        <v>1101</v>
-      </c>
-      <c r="E350" s="61"/>
-      <c r="I350" s="65"/>
-      <c r="J350" s="66"/>
+      <c r="D350" s="60" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E350" s="60"/>
+      <c r="I350" s="64"/>
+      <c r="J350" s="65"/>
       <c r="K350" s="8"/>
       <c r="L350" s="8"/>
-      <c r="M350" s="65"/>
-      <c r="N350" s="65"/>
+      <c r="M350" s="64"/>
+      <c r="N350" s="64"/>
       <c r="O350" s="8"/>
-      <c r="P350" s="65"/>
+      <c r="P350" s="64"/>
       <c r="S350" s="42"/>
       <c r="T350" s="41">
         <v>61</v>
       </c>
-      <c r="U350" s="58" t="s">
+      <c r="U350" s="57" t="s">
         <v>730</v>
       </c>
-      <c r="V350" s="58"/>
+      <c r="V350" s="57"/>
       <c r="W350" s="10"/>
       <c r="X350" s="3"/>
       <c r="Y350" s="10"/>
@@ -28299,8 +28380,8 @@
       <c r="AF350" s="11"/>
       <c r="AI350" s="3"/>
       <c r="AJ350" s="3"/>
-      <c r="AK350" s="56" t="s">
-        <v>1113</v>
+      <c r="AK350" s="55" t="s">
+        <v>1112</v>
       </c>
       <c r="AL350" s="42" t="s">
         <v>654</v>
@@ -28311,39 +28392,39 @@
     </row>
     <row r="351" spans="1:39" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="38" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B351" s="37" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="C351" s="38" t="s">
         <v>13</v>
       </c>
       <c r="D351" s="37"/>
       <c r="E351" s="37" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F351" s="42" t="s">
         <v>15</v>
       </c>
       <c r="G351" s="37" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H351" s="39">
         <v>22</v>
       </c>
       <c r="I351" s="42"/>
       <c r="J351" s="40"/>
-      <c r="K351" s="50"/>
-      <c r="L351" s="50"/>
+      <c r="K351" s="49"/>
+      <c r="L351" s="49"/>
       <c r="M351" s="42" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="N351" s="42" t="s">
         <v>591</v>
       </c>
-      <c r="O351" s="67" t="s">
-        <v>1115</v>
+      <c r="O351" s="66" t="s">
+        <v>1114</v>
       </c>
       <c r="P351" s="42" t="s">
         <v>600</v>
@@ -28356,15 +28437,15 @@
       <c r="T351" s="41">
         <v>23</v>
       </c>
-      <c r="U351" s="58" t="s">
+      <c r="U351" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="V351" s="58"/>
+      <c r="V351" s="57"/>
       <c r="X351" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AK351" s="60" t="s">
-        <v>1114</v>
+      <c r="AK351" s="59" t="s">
+        <v>1113</v>
       </c>
       <c r="AL351" s="42" t="s">
         <v>654</v>
@@ -28376,708 +28457,708 @@
     <row r="352" spans="1:39" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F352" s="48"/>
       <c r="J352" s="48"/>
-      <c r="K352" s="50"/>
-      <c r="L352" s="50"/>
-      <c r="O352" s="50"/>
+      <c r="K352" s="49"/>
+      <c r="L352" s="49"/>
+      <c r="O352" s="49"/>
     </row>
     <row r="353" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F353" s="48"/>
       <c r="J353" s="48"/>
-      <c r="K353" s="50"/>
-      <c r="L353" s="50"/>
-      <c r="O353" s="50"/>
+      <c r="K353" s="49"/>
+      <c r="L353" s="49"/>
+      <c r="O353" s="49"/>
     </row>
     <row r="354" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F354" s="48"/>
       <c r="J354" s="48"/>
-      <c r="K354" s="50"/>
-      <c r="L354" s="50"/>
-      <c r="O354" s="50"/>
+      <c r="K354" s="49"/>
+      <c r="L354" s="49"/>
+      <c r="O354" s="49"/>
     </row>
     <row r="355" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F355" s="48"/>
       <c r="J355" s="48"/>
-      <c r="K355" s="50"/>
-      <c r="L355" s="50"/>
-      <c r="O355" s="50"/>
+      <c r="K355" s="49"/>
+      <c r="L355" s="49"/>
+      <c r="O355" s="49"/>
     </row>
     <row r="356" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F356" s="48"/>
       <c r="J356" s="48"/>
-      <c r="K356" s="50"/>
-      <c r="L356" s="50"/>
-      <c r="O356" s="50"/>
+      <c r="K356" s="49"/>
+      <c r="L356" s="49"/>
+      <c r="O356" s="49"/>
     </row>
     <row r="357" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F357" s="48"/>
       <c r="J357" s="48"/>
-      <c r="K357" s="50"/>
-      <c r="L357" s="50"/>
-      <c r="O357" s="50"/>
+      <c r="K357" s="49"/>
+      <c r="L357" s="49"/>
+      <c r="O357" s="49"/>
     </row>
     <row r="358" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F358" s="48"/>
       <c r="J358" s="48"/>
-      <c r="K358" s="50"/>
-      <c r="L358" s="50"/>
-      <c r="O358" s="50"/>
+      <c r="K358" s="49"/>
+      <c r="L358" s="49"/>
+      <c r="O358" s="49"/>
     </row>
     <row r="359" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F359" s="48"/>
       <c r="J359" s="48"/>
-      <c r="K359" s="50"/>
-      <c r="L359" s="50"/>
-      <c r="O359" s="50"/>
+      <c r="K359" s="49"/>
+      <c r="L359" s="49"/>
+      <c r="O359" s="49"/>
     </row>
     <row r="360" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F360" s="48"/>
       <c r="J360" s="48"/>
-      <c r="K360" s="50"/>
-      <c r="L360" s="50"/>
-      <c r="O360" s="50"/>
+      <c r="K360" s="49"/>
+      <c r="L360" s="49"/>
+      <c r="O360" s="49"/>
     </row>
     <row r="361" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F361" s="48"/>
       <c r="J361" s="48"/>
-      <c r="K361" s="50"/>
-      <c r="L361" s="50"/>
-      <c r="O361" s="50"/>
+      <c r="K361" s="49"/>
+      <c r="L361" s="49"/>
+      <c r="O361" s="49"/>
     </row>
     <row r="362" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F362" s="48"/>
       <c r="J362" s="48"/>
-      <c r="K362" s="50"/>
-      <c r="L362" s="50"/>
-      <c r="O362" s="50"/>
+      <c r="K362" s="49"/>
+      <c r="L362" s="49"/>
+      <c r="O362" s="49"/>
     </row>
     <row r="363" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F363" s="48"/>
       <c r="J363" s="48"/>
-      <c r="K363" s="50"/>
-      <c r="L363" s="50"/>
-      <c r="O363" s="50"/>
+      <c r="K363" s="49"/>
+      <c r="L363" s="49"/>
+      <c r="O363" s="49"/>
     </row>
     <row r="364" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F364" s="48"/>
       <c r="J364" s="48"/>
-      <c r="K364" s="50"/>
-      <c r="L364" s="50"/>
-      <c r="O364" s="50"/>
+      <c r="K364" s="49"/>
+      <c r="L364" s="49"/>
+      <c r="O364" s="49"/>
     </row>
     <row r="365" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F365" s="48"/>
       <c r="J365" s="48"/>
-      <c r="K365" s="50"/>
-      <c r="L365" s="50"/>
-      <c r="O365" s="50"/>
+      <c r="K365" s="49"/>
+      <c r="L365" s="49"/>
+      <c r="O365" s="49"/>
     </row>
     <row r="366" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F366" s="48"/>
       <c r="J366" s="48"/>
-      <c r="K366" s="50"/>
-      <c r="L366" s="50"/>
-      <c r="O366" s="50"/>
+      <c r="K366" s="49"/>
+      <c r="L366" s="49"/>
+      <c r="O366" s="49"/>
     </row>
     <row r="367" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F367" s="48"/>
       <c r="J367" s="48"/>
-      <c r="K367" s="50"/>
-      <c r="L367" s="50"/>
-      <c r="O367" s="50"/>
+      <c r="K367" s="49"/>
+      <c r="L367" s="49"/>
+      <c r="O367" s="49"/>
     </row>
     <row r="368" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F368" s="48"/>
       <c r="J368" s="48"/>
-      <c r="K368" s="50"/>
-      <c r="L368" s="50"/>
-      <c r="O368" s="50"/>
+      <c r="K368" s="49"/>
+      <c r="L368" s="49"/>
+      <c r="O368" s="49"/>
     </row>
     <row r="369" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F369" s="48"/>
       <c r="J369" s="48"/>
-      <c r="K369" s="50"/>
-      <c r="L369" s="50"/>
-      <c r="O369" s="50"/>
+      <c r="K369" s="49"/>
+      <c r="L369" s="49"/>
+      <c r="O369" s="49"/>
     </row>
     <row r="370" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F370" s="48"/>
       <c r="J370" s="48"/>
-      <c r="K370" s="50"/>
-      <c r="L370" s="50"/>
-      <c r="O370" s="50"/>
+      <c r="K370" s="49"/>
+      <c r="L370" s="49"/>
+      <c r="O370" s="49"/>
     </row>
     <row r="371" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F371" s="48"/>
       <c r="J371" s="48"/>
-      <c r="K371" s="50"/>
-      <c r="L371" s="50"/>
-      <c r="O371" s="50"/>
+      <c r="K371" s="49"/>
+      <c r="L371" s="49"/>
+      <c r="O371" s="49"/>
     </row>
     <row r="372" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F372" s="48"/>
       <c r="J372" s="48"/>
-      <c r="K372" s="50"/>
-      <c r="L372" s="50"/>
-      <c r="O372" s="50"/>
+      <c r="K372" s="49"/>
+      <c r="L372" s="49"/>
+      <c r="O372" s="49"/>
     </row>
     <row r="373" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F373" s="48"/>
       <c r="J373" s="48"/>
-      <c r="K373" s="50"/>
-      <c r="L373" s="50"/>
-      <c r="O373" s="50"/>
+      <c r="K373" s="49"/>
+      <c r="L373" s="49"/>
+      <c r="O373" s="49"/>
     </row>
     <row r="374" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F374" s="48"/>
       <c r="J374" s="48"/>
-      <c r="K374" s="50"/>
-      <c r="L374" s="50"/>
-      <c r="O374" s="50"/>
+      <c r="K374" s="49"/>
+      <c r="L374" s="49"/>
+      <c r="O374" s="49"/>
     </row>
     <row r="375" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F375" s="48"/>
       <c r="J375" s="48"/>
-      <c r="K375" s="50"/>
-      <c r="L375" s="50"/>
-      <c r="O375" s="50"/>
+      <c r="K375" s="49"/>
+      <c r="L375" s="49"/>
+      <c r="O375" s="49"/>
     </row>
     <row r="376" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F376" s="48"/>
       <c r="J376" s="48"/>
-      <c r="K376" s="50"/>
-      <c r="L376" s="50"/>
-      <c r="O376" s="50"/>
+      <c r="K376" s="49"/>
+      <c r="L376" s="49"/>
+      <c r="O376" s="49"/>
     </row>
     <row r="377" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F377" s="48"/>
       <c r="J377" s="48"/>
-      <c r="K377" s="50"/>
-      <c r="L377" s="50"/>
-      <c r="O377" s="50"/>
+      <c r="K377" s="49"/>
+      <c r="L377" s="49"/>
+      <c r="O377" s="49"/>
     </row>
     <row r="378" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F378" s="48"/>
       <c r="J378" s="48"/>
-      <c r="K378" s="50"/>
-      <c r="L378" s="50"/>
-      <c r="O378" s="50"/>
+      <c r="K378" s="49"/>
+      <c r="L378" s="49"/>
+      <c r="O378" s="49"/>
     </row>
     <row r="379" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F379" s="48"/>
       <c r="J379" s="48"/>
-      <c r="K379" s="50"/>
-      <c r="L379" s="50"/>
-      <c r="O379" s="50"/>
+      <c r="K379" s="49"/>
+      <c r="L379" s="49"/>
+      <c r="O379" s="49"/>
     </row>
     <row r="380" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F380" s="48"/>
       <c r="J380" s="48"/>
-      <c r="K380" s="50"/>
-      <c r="L380" s="50"/>
-      <c r="O380" s="50"/>
+      <c r="K380" s="49"/>
+      <c r="L380" s="49"/>
+      <c r="O380" s="49"/>
     </row>
     <row r="381" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F381" s="48"/>
       <c r="J381" s="48"/>
-      <c r="K381" s="50"/>
-      <c r="L381" s="50"/>
-      <c r="O381" s="50"/>
+      <c r="K381" s="49"/>
+      <c r="L381" s="49"/>
+      <c r="O381" s="49"/>
     </row>
     <row r="382" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F382" s="48"/>
       <c r="J382" s="48"/>
-      <c r="K382" s="50"/>
-      <c r="L382" s="50"/>
-      <c r="O382" s="50"/>
+      <c r="K382" s="49"/>
+      <c r="L382" s="49"/>
+      <c r="O382" s="49"/>
     </row>
     <row r="383" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F383" s="48"/>
       <c r="J383" s="48"/>
-      <c r="K383" s="50"/>
-      <c r="L383" s="50"/>
-      <c r="O383" s="50"/>
+      <c r="K383" s="49"/>
+      <c r="L383" s="49"/>
+      <c r="O383" s="49"/>
     </row>
     <row r="384" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F384" s="48"/>
       <c r="J384" s="48"/>
-      <c r="K384" s="50"/>
-      <c r="L384" s="50"/>
-      <c r="O384" s="50"/>
+      <c r="K384" s="49"/>
+      <c r="L384" s="49"/>
+      <c r="O384" s="49"/>
     </row>
     <row r="385" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F385" s="48"/>
       <c r="J385" s="48"/>
-      <c r="K385" s="50"/>
-      <c r="L385" s="50"/>
-      <c r="O385" s="50"/>
+      <c r="K385" s="49"/>
+      <c r="L385" s="49"/>
+      <c r="O385" s="49"/>
     </row>
     <row r="386" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F386" s="48"/>
       <c r="J386" s="48"/>
-      <c r="K386" s="50"/>
-      <c r="L386" s="50"/>
-      <c r="O386" s="50"/>
+      <c r="K386" s="49"/>
+      <c r="L386" s="49"/>
+      <c r="O386" s="49"/>
     </row>
     <row r="387" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F387" s="48"/>
       <c r="J387" s="48"/>
-      <c r="K387" s="50"/>
-      <c r="L387" s="50"/>
-      <c r="O387" s="50"/>
+      <c r="K387" s="49"/>
+      <c r="L387" s="49"/>
+      <c r="O387" s="49"/>
     </row>
     <row r="388" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F388" s="48"/>
       <c r="J388" s="48"/>
-      <c r="K388" s="50"/>
-      <c r="L388" s="50"/>
-      <c r="O388" s="50"/>
+      <c r="K388" s="49"/>
+      <c r="L388" s="49"/>
+      <c r="O388" s="49"/>
     </row>
     <row r="389" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F389" s="48"/>
       <c r="J389" s="48"/>
-      <c r="K389" s="50"/>
-      <c r="L389" s="50"/>
-      <c r="O389" s="50"/>
+      <c r="K389" s="49"/>
+      <c r="L389" s="49"/>
+      <c r="O389" s="49"/>
     </row>
     <row r="390" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F390" s="48"/>
       <c r="J390" s="48"/>
-      <c r="K390" s="50"/>
-      <c r="L390" s="50"/>
-      <c r="O390" s="50"/>
+      <c r="K390" s="49"/>
+      <c r="L390" s="49"/>
+      <c r="O390" s="49"/>
     </row>
     <row r="391" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F391" s="48"/>
       <c r="J391" s="48"/>
-      <c r="K391" s="50"/>
-      <c r="L391" s="50"/>
-      <c r="O391" s="50"/>
+      <c r="K391" s="49"/>
+      <c r="L391" s="49"/>
+      <c r="O391" s="49"/>
     </row>
     <row r="392" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F392" s="48"/>
       <c r="J392" s="48"/>
-      <c r="K392" s="50"/>
-      <c r="L392" s="50"/>
+      <c r="K392" s="49"/>
+      <c r="L392" s="49"/>
     </row>
     <row r="393" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F393" s="48"/>
       <c r="J393" s="48"/>
-      <c r="K393" s="50"/>
-      <c r="L393" s="50"/>
+      <c r="K393" s="49"/>
+      <c r="L393" s="49"/>
     </row>
     <row r="394" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F394" s="48"/>
       <c r="J394" s="48"/>
-      <c r="K394" s="50"/>
-      <c r="L394" s="50"/>
+      <c r="K394" s="49"/>
+      <c r="L394" s="49"/>
     </row>
     <row r="395" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F395" s="48"/>
       <c r="J395" s="48"/>
-      <c r="K395" s="50"/>
-      <c r="L395" s="50"/>
+      <c r="K395" s="49"/>
+      <c r="L395" s="49"/>
     </row>
     <row r="396" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F396" s="48"/>
       <c r="J396" s="48"/>
-      <c r="K396" s="50"/>
-      <c r="L396" s="50"/>
+      <c r="K396" s="49"/>
+      <c r="L396" s="49"/>
     </row>
     <row r="397" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F397" s="48"/>
       <c r="J397" s="48"/>
-      <c r="K397" s="50"/>
-      <c r="L397" s="50"/>
+      <c r="K397" s="49"/>
+      <c r="L397" s="49"/>
     </row>
     <row r="398" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F398" s="48"/>
       <c r="J398" s="48"/>
-      <c r="K398" s="50"/>
-      <c r="L398" s="50"/>
+      <c r="K398" s="49"/>
+      <c r="L398" s="49"/>
     </row>
     <row r="399" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F399" s="48"/>
       <c r="J399" s="48"/>
-      <c r="K399" s="50"/>
-      <c r="L399" s="50"/>
+      <c r="K399" s="49"/>
+      <c r="L399" s="49"/>
     </row>
     <row r="400" spans="6:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F400" s="48"/>
       <c r="J400" s="48"/>
-      <c r="K400" s="50"/>
-      <c r="L400" s="50"/>
+      <c r="K400" s="49"/>
+      <c r="L400" s="49"/>
     </row>
     <row r="401" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F401" s="48"/>
       <c r="J401" s="48"/>
-      <c r="K401" s="50"/>
-      <c r="L401" s="50"/>
+      <c r="K401" s="49"/>
+      <c r="L401" s="49"/>
     </row>
     <row r="402" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F402" s="48"/>
       <c r="J402" s="48"/>
-      <c r="K402" s="50"/>
-      <c r="L402" s="50"/>
+      <c r="K402" s="49"/>
+      <c r="L402" s="49"/>
     </row>
     <row r="403" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F403" s="48"/>
       <c r="J403" s="48"/>
-      <c r="K403" s="50"/>
-      <c r="L403" s="50"/>
+      <c r="K403" s="49"/>
+      <c r="L403" s="49"/>
     </row>
     <row r="404" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F404" s="48"/>
       <c r="J404" s="48"/>
-      <c r="K404" s="50"/>
-      <c r="L404" s="50"/>
+      <c r="K404" s="49"/>
+      <c r="L404" s="49"/>
     </row>
     <row r="405" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F405" s="48"/>
       <c r="J405" s="48"/>
-      <c r="K405" s="50"/>
-      <c r="L405" s="50"/>
+      <c r="K405" s="49"/>
+      <c r="L405" s="49"/>
     </row>
     <row r="406" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F406" s="48"/>
       <c r="J406" s="48"/>
-      <c r="K406" s="50"/>
-      <c r="L406" s="50"/>
+      <c r="K406" s="49"/>
+      <c r="L406" s="49"/>
     </row>
     <row r="407" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F407" s="48"/>
       <c r="J407" s="48"/>
-      <c r="K407" s="50"/>
-      <c r="L407" s="50"/>
+      <c r="K407" s="49"/>
+      <c r="L407" s="49"/>
     </row>
     <row r="408" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F408" s="48"/>
       <c r="J408" s="48"/>
-      <c r="K408" s="50"/>
-      <c r="L408" s="50"/>
+      <c r="K408" s="49"/>
+      <c r="L408" s="49"/>
     </row>
     <row r="409" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F409" s="48"/>
       <c r="J409" s="48"/>
-      <c r="K409" s="50"/>
-      <c r="L409" s="50"/>
+      <c r="K409" s="49"/>
+      <c r="L409" s="49"/>
     </row>
     <row r="410" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F410" s="48"/>
       <c r="J410" s="48"/>
-      <c r="K410" s="50"/>
-      <c r="L410" s="50"/>
+      <c r="K410" s="49"/>
+      <c r="L410" s="49"/>
     </row>
     <row r="411" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F411" s="48"/>
       <c r="J411" s="48"/>
-      <c r="K411" s="50"/>
-      <c r="L411" s="50"/>
+      <c r="K411" s="49"/>
+      <c r="L411" s="49"/>
     </row>
     <row r="412" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F412" s="48"/>
       <c r="J412" s="48"/>
-      <c r="K412" s="50"/>
-      <c r="L412" s="50"/>
+      <c r="K412" s="49"/>
+      <c r="L412" s="49"/>
     </row>
     <row r="413" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F413" s="48"/>
       <c r="J413" s="48"/>
-      <c r="K413" s="50"/>
-      <c r="L413" s="50"/>
+      <c r="K413" s="49"/>
+      <c r="L413" s="49"/>
     </row>
     <row r="414" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F414" s="48"/>
       <c r="J414" s="48"/>
-      <c r="K414" s="50"/>
-      <c r="L414" s="50"/>
+      <c r="K414" s="49"/>
+      <c r="L414" s="49"/>
     </row>
     <row r="415" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F415" s="48"/>
       <c r="J415" s="48"/>
-      <c r="K415" s="50"/>
-      <c r="L415" s="50"/>
+      <c r="K415" s="49"/>
+      <c r="L415" s="49"/>
     </row>
     <row r="416" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F416" s="48"/>
       <c r="J416" s="48"/>
-      <c r="K416" s="50"/>
-      <c r="L416" s="50"/>
+      <c r="K416" s="49"/>
+      <c r="L416" s="49"/>
     </row>
     <row r="417" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F417" s="48"/>
       <c r="J417" s="48"/>
-      <c r="K417" s="50"/>
-      <c r="L417" s="50"/>
+      <c r="K417" s="49"/>
+      <c r="L417" s="49"/>
     </row>
     <row r="418" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F418" s="48"/>
       <c r="J418" s="48"/>
-      <c r="K418" s="50"/>
-      <c r="L418" s="50"/>
+      <c r="K418" s="49"/>
+      <c r="L418" s="49"/>
     </row>
     <row r="419" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F419" s="48"/>
       <c r="J419" s="48"/>
-      <c r="K419" s="50"/>
-      <c r="L419" s="50"/>
+      <c r="K419" s="49"/>
+      <c r="L419" s="49"/>
     </row>
     <row r="420" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F420" s="48"/>
       <c r="J420" s="48"/>
-      <c r="K420" s="50"/>
-      <c r="L420" s="50"/>
+      <c r="K420" s="49"/>
+      <c r="L420" s="49"/>
     </row>
     <row r="421" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F421" s="48"/>
       <c r="J421" s="48"/>
-      <c r="K421" s="50"/>
-      <c r="L421" s="50"/>
+      <c r="K421" s="49"/>
+      <c r="L421" s="49"/>
     </row>
     <row r="422" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F422" s="48"/>
       <c r="J422" s="48"/>
-      <c r="K422" s="50"/>
-      <c r="L422" s="50"/>
+      <c r="K422" s="49"/>
+      <c r="L422" s="49"/>
     </row>
     <row r="423" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F423" s="48"/>
       <c r="J423" s="48"/>
-      <c r="K423" s="50"/>
-      <c r="L423" s="50"/>
+      <c r="K423" s="49"/>
+      <c r="L423" s="49"/>
     </row>
     <row r="424" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F424" s="48"/>
       <c r="J424" s="48"/>
-      <c r="K424" s="50"/>
-      <c r="L424" s="50"/>
+      <c r="K424" s="49"/>
+      <c r="L424" s="49"/>
     </row>
     <row r="425" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F425" s="48"/>
       <c r="J425" s="48"/>
-      <c r="K425" s="50"/>
-      <c r="L425" s="50"/>
+      <c r="K425" s="49"/>
+      <c r="L425" s="49"/>
     </row>
     <row r="426" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F426" s="48"/>
       <c r="J426" s="48"/>
-      <c r="K426" s="50"/>
-      <c r="L426" s="50"/>
+      <c r="K426" s="49"/>
+      <c r="L426" s="49"/>
     </row>
     <row r="427" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F427" s="48"/>
       <c r="J427" s="48"/>
-      <c r="K427" s="50"/>
-      <c r="L427" s="50"/>
+      <c r="K427" s="49"/>
+      <c r="L427" s="49"/>
     </row>
     <row r="428" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F428" s="48"/>
       <c r="J428" s="48"/>
-      <c r="K428" s="50"/>
-      <c r="L428" s="50"/>
+      <c r="K428" s="49"/>
+      <c r="L428" s="49"/>
     </row>
     <row r="429" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F429" s="48"/>
       <c r="J429" s="48"/>
-      <c r="K429" s="50"/>
-      <c r="L429" s="50"/>
+      <c r="K429" s="49"/>
+      <c r="L429" s="49"/>
     </row>
     <row r="430" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F430" s="48"/>
       <c r="J430" s="48"/>
-      <c r="K430" s="50"/>
-      <c r="L430" s="50"/>
+      <c r="K430" s="49"/>
+      <c r="L430" s="49"/>
     </row>
     <row r="431" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F431" s="48"/>
       <c r="J431" s="48"/>
-      <c r="K431" s="50"/>
-      <c r="L431" s="50"/>
+      <c r="K431" s="49"/>
+      <c r="L431" s="49"/>
     </row>
     <row r="432" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F432" s="48"/>
       <c r="J432" s="48"/>
-      <c r="K432" s="50"/>
-      <c r="L432" s="50"/>
+      <c r="K432" s="49"/>
+      <c r="L432" s="49"/>
     </row>
     <row r="433" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F433" s="48"/>
       <c r="J433" s="48"/>
-      <c r="K433" s="50"/>
-      <c r="L433" s="50"/>
+      <c r="K433" s="49"/>
+      <c r="L433" s="49"/>
     </row>
     <row r="434" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F434" s="48"/>
       <c r="J434" s="48"/>
-      <c r="K434" s="50"/>
-      <c r="L434" s="50"/>
+      <c r="K434" s="49"/>
+      <c r="L434" s="49"/>
     </row>
     <row r="435" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F435" s="48"/>
       <c r="J435" s="48"/>
-      <c r="K435" s="50"/>
-      <c r="L435" s="50"/>
+      <c r="K435" s="49"/>
+      <c r="L435" s="49"/>
     </row>
     <row r="436" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F436" s="48"/>
       <c r="J436" s="48"/>
-      <c r="K436" s="50"/>
-      <c r="L436" s="50"/>
+      <c r="K436" s="49"/>
+      <c r="L436" s="49"/>
     </row>
     <row r="437" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F437" s="48"/>
       <c r="J437" s="48"/>
-      <c r="K437" s="50"/>
-      <c r="L437" s="50"/>
+      <c r="K437" s="49"/>
+      <c r="L437" s="49"/>
     </row>
     <row r="438" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F438" s="48"/>
       <c r="J438" s="48"/>
-      <c r="K438" s="50"/>
-      <c r="L438" s="50"/>
+      <c r="K438" s="49"/>
+      <c r="L438" s="49"/>
     </row>
     <row r="439" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F439" s="48"/>
       <c r="J439" s="48"/>
-      <c r="K439" s="50"/>
-      <c r="L439" s="50"/>
+      <c r="K439" s="49"/>
+      <c r="L439" s="49"/>
     </row>
     <row r="440" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F440" s="48"/>
       <c r="J440" s="48"/>
-      <c r="K440" s="50"/>
-      <c r="L440" s="50"/>
+      <c r="K440" s="49"/>
+      <c r="L440" s="49"/>
     </row>
     <row r="441" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F441" s="48"/>
       <c r="J441" s="48"/>
-      <c r="K441" s="50"/>
-      <c r="L441" s="50"/>
+      <c r="K441" s="49"/>
+      <c r="L441" s="49"/>
     </row>
     <row r="442" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F442" s="48"/>
       <c r="J442" s="48"/>
-      <c r="K442" s="50"/>
-      <c r="L442" s="50"/>
+      <c r="K442" s="49"/>
+      <c r="L442" s="49"/>
     </row>
     <row r="443" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F443" s="48"/>
       <c r="J443" s="48"/>
-      <c r="K443" s="50"/>
-      <c r="L443" s="50"/>
+      <c r="K443" s="49"/>
+      <c r="L443" s="49"/>
     </row>
     <row r="444" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F444" s="48"/>
       <c r="J444" s="48"/>
-      <c r="K444" s="50"/>
-      <c r="L444" s="50"/>
+      <c r="K444" s="49"/>
+      <c r="L444" s="49"/>
     </row>
     <row r="445" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F445" s="48"/>
       <c r="J445" s="48"/>
-      <c r="K445" s="50"/>
-      <c r="L445" s="50"/>
+      <c r="K445" s="49"/>
+      <c r="L445" s="49"/>
     </row>
     <row r="446" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F446" s="48"/>
       <c r="J446" s="48"/>
-      <c r="K446" s="50"/>
-      <c r="L446" s="50"/>
+      <c r="K446" s="49"/>
+      <c r="L446" s="49"/>
     </row>
     <row r="447" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F447" s="48"/>
       <c r="J447" s="48"/>
-      <c r="K447" s="50"/>
-      <c r="L447" s="50"/>
+      <c r="K447" s="49"/>
+      <c r="L447" s="49"/>
     </row>
     <row r="448" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F448" s="48"/>
       <c r="J448" s="48"/>
-      <c r="K448" s="50"/>
-      <c r="L448" s="50"/>
+      <c r="K448" s="49"/>
+      <c r="L448" s="49"/>
     </row>
     <row r="449" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F449" s="48"/>
       <c r="J449" s="48"/>
-      <c r="K449" s="50"/>
-      <c r="L449" s="50"/>
+      <c r="K449" s="49"/>
+      <c r="L449" s="49"/>
     </row>
     <row r="450" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F450" s="48"/>
       <c r="J450" s="48"/>
-      <c r="K450" s="50"/>
-      <c r="L450" s="50"/>
+      <c r="K450" s="49"/>
+      <c r="L450" s="49"/>
     </row>
     <row r="451" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F451" s="48"/>
       <c r="J451" s="48"/>
-      <c r="K451" s="50"/>
-      <c r="L451" s="50"/>
+      <c r="K451" s="49"/>
+      <c r="L451" s="49"/>
     </row>
     <row r="452" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F452" s="48"/>
       <c r="J452" s="48"/>
-      <c r="K452" s="50"/>
-      <c r="L452" s="50"/>
+      <c r="K452" s="49"/>
+      <c r="L452" s="49"/>
     </row>
     <row r="453" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F453" s="48"/>
       <c r="J453" s="48"/>
-      <c r="K453" s="50"/>
-      <c r="L453" s="50"/>
+      <c r="K453" s="49"/>
+      <c r="L453" s="49"/>
     </row>
     <row r="454" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F454" s="48"/>
       <c r="J454" s="48"/>
-      <c r="K454" s="50"/>
-      <c r="L454" s="50"/>
+      <c r="K454" s="49"/>
+      <c r="L454" s="49"/>
     </row>
     <row r="455" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F455" s="48"/>
       <c r="J455" s="48"/>
-      <c r="K455" s="50"/>
-      <c r="L455" s="50"/>
+      <c r="K455" s="49"/>
+      <c r="L455" s="49"/>
     </row>
     <row r="456" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F456" s="48"/>
       <c r="J456" s="48"/>
-      <c r="K456" s="50"/>
-      <c r="L456" s="50"/>
+      <c r="K456" s="49"/>
+      <c r="L456" s="49"/>
     </row>
     <row r="457" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F457" s="48"/>
       <c r="J457" s="48"/>
-      <c r="K457" s="50"/>
-      <c r="L457" s="50"/>
+      <c r="K457" s="49"/>
+      <c r="L457" s="49"/>
     </row>
     <row r="458" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F458" s="48"/>
       <c r="J458" s="48"/>
-      <c r="K458" s="50"/>
-      <c r="L458" s="50"/>
+      <c r="K458" s="49"/>
+      <c r="L458" s="49"/>
     </row>
     <row r="459" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F459" s="48"/>
       <c r="J459" s="48"/>
-      <c r="K459" s="50"/>
-      <c r="L459" s="50"/>
+      <c r="K459" s="49"/>
+      <c r="L459" s="49"/>
     </row>
     <row r="460" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F460" s="48"/>
       <c r="J460" s="48"/>
-      <c r="K460" s="50"/>
-      <c r="L460" s="50"/>
+      <c r="K460" s="49"/>
+      <c r="L460" s="49"/>
     </row>
     <row r="461" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F461" s="48"/>
       <c r="J461" s="48"/>
-      <c r="K461" s="50"/>
-      <c r="L461" s="50"/>
+      <c r="K461" s="49"/>
+      <c r="L461" s="49"/>
     </row>
     <row r="462" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F462" s="48"/>
       <c r="J462" s="48"/>
-      <c r="K462" s="50"/>
-      <c r="L462" s="50"/>
+      <c r="K462" s="49"/>
+      <c r="L462" s="49"/>
     </row>
     <row r="463" spans="6:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F463" s="48"/>
@@ -29100,13 +29181,13 @@
           <x14:formula1>
             <xm:f>Sheet2!$A$1:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>AH51:AH57 AH2:AH50</xm:sqref>
+          <xm:sqref>AH2:AH57</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{613416C5-79E4-9B4F-AAC7-C5212E6DD24E}">
           <x14:formula1>
             <xm:f>Sheet2!$B$1:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>AI51:AI351 AI2:AI50</xm:sqref>
+          <xm:sqref>AI2:AI351</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
